--- a/research/traditional_assets/database/data/india/india_retail_rei_ts.xlsx
+++ b/research/traditional_assets/database/data/india/india_retail_rei_ts.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08932160355190145</v>
+        <v>0.08908513874124574</v>
       </c>
       <c r="C2">
-        <v>2901.96971296752</v>
+        <v>2885.617130732065</v>
       </c>
       <c r="D2">
-        <v>2900.25971296752</v>
+        <v>2913.237130732065</v>
       </c>
       <c r="E2">
-        <v>-521.7</v>
+        <v>-492.3700000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29.33</v>
       </c>
       <c r="G2">
         <v>1.71</v>
@@ -1445,28 +1445,28 @@
         <v>157.65</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.475299</v>
       </c>
       <c r="N2">
-        <v>157.65</v>
+        <v>156.174701</v>
       </c>
       <c r="O2">
-        <v>47.29499999999999</v>
+        <v>46.85241029999999</v>
       </c>
       <c r="P2">
-        <v>110.355</v>
+        <v>109.3222907</v>
       </c>
       <c r="Q2">
-        <v>180.455</v>
+        <v>179.4222907</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08932160355190145</v>
+        <v>0.08962933206186439</v>
       </c>
       <c r="T2">
-        <v>0.5990912546403601</v>
+        <v>0.6033272534105444</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>106.8596942043613</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08908513874124574</v>
+        <v>0.08884867393059005</v>
       </c>
       <c r="C3">
-        <v>2885.617130732065</v>
+        <v>2869.381207246683</v>
       </c>
       <c r="D3">
-        <v>2913.237130732065</v>
+        <v>2926.331207246683</v>
       </c>
       <c r="E3">
-        <v>-492.3700000000001</v>
+        <v>-463.04</v>
       </c>
       <c r="F3">
-        <v>29.33</v>
+        <v>58.66</v>
       </c>
       <c r="G3">
         <v>1.71</v>
@@ -1527,28 +1527,28 @@
         <v>157.65</v>
       </c>
       <c r="M3">
-        <v>1.475299</v>
+        <v>2.950598</v>
       </c>
       <c r="N3">
-        <v>156.174701</v>
+        <v>154.699402</v>
       </c>
       <c r="O3">
-        <v>46.85241029999999</v>
+        <v>46.40982059999999</v>
       </c>
       <c r="P3">
-        <v>109.3222907</v>
+        <v>108.2895814</v>
       </c>
       <c r="Q3">
-        <v>179.4222907</v>
+        <v>178.3895814</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08962933206186439</v>
+        <v>0.08994334074550005</v>
       </c>
       <c r="T3">
-        <v>0.6033272534105444</v>
+        <v>0.6076497011352223</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>106.8596942043613</v>
+        <v>53.42984710218063</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08884867393059005</v>
+        <v>0.08861220911993434</v>
       </c>
       <c r="C4">
-        <v>2869.381207246683</v>
+        <v>2853.263522645775</v>
       </c>
       <c r="D4">
-        <v>2926.331207246683</v>
+        <v>2939.543522645775</v>
       </c>
       <c r="E4">
-        <v>-463.04</v>
+        <v>-433.71</v>
       </c>
       <c r="F4">
-        <v>58.66</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="G4">
         <v>1.71</v>
@@ -1609,28 +1609,28 @@
         <v>157.65</v>
       </c>
       <c r="M4">
-        <v>2.950598</v>
+        <v>4.425896999999999</v>
       </c>
       <c r="N4">
-        <v>154.699402</v>
+        <v>153.224103</v>
       </c>
       <c r="O4">
-        <v>46.40982059999999</v>
+        <v>45.9672309</v>
       </c>
       <c r="P4">
-        <v>108.2895814</v>
+        <v>107.2568721</v>
       </c>
       <c r="Q4">
-        <v>178.3895814</v>
+        <v>177.3568721</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08994334074550005</v>
+        <v>0.09026382383498385</v>
       </c>
       <c r="T4">
-        <v>0.6076497011352223</v>
+        <v>0.6120612714933987</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>53.42984710218063</v>
+        <v>35.61989806812043</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08861220911993434</v>
+        <v>0.08837574430927864</v>
       </c>
       <c r="C5">
-        <v>2853.263522645775</v>
+        <v>2837.265685730241</v>
       </c>
       <c r="D5">
-        <v>2939.543522645775</v>
+        <v>2952.875685730241</v>
       </c>
       <c r="E5">
-        <v>-433.71</v>
+        <v>-404.3800000000001</v>
       </c>
       <c r="F5">
-        <v>87.98999999999999</v>
+        <v>117.32</v>
       </c>
       <c r="G5">
         <v>1.71</v>
@@ -1691,28 +1691,28 @@
         <v>157.65</v>
       </c>
       <c r="M5">
-        <v>4.425896999999999</v>
+        <v>5.901196</v>
       </c>
       <c r="N5">
-        <v>153.224103</v>
+        <v>151.748804</v>
       </c>
       <c r="O5">
-        <v>45.9672309</v>
+        <v>45.52464119999999</v>
       </c>
       <c r="P5">
-        <v>107.2568721</v>
+        <v>106.2241628</v>
       </c>
       <c r="Q5">
-        <v>177.3568721</v>
+        <v>176.3241628</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09026382383498385</v>
+        <v>0.09059098365549859</v>
       </c>
       <c r="T5">
-        <v>0.6120612714933987</v>
+        <v>0.6165647495673705</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>35.61989806812043</v>
+        <v>26.71492355109032</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08837574430927864</v>
+        <v>0.08813927949862292</v>
       </c>
       <c r="C6">
-        <v>2837.265685730241</v>
+        <v>2821.38933462053</v>
       </c>
       <c r="D6">
-        <v>2952.875685730241</v>
+        <v>2966.329334620531</v>
       </c>
       <c r="E6">
-        <v>-404.3800000000001</v>
+        <v>-375.0500000000001</v>
       </c>
       <c r="F6">
-        <v>117.32</v>
+        <v>146.65</v>
       </c>
       <c r="G6">
         <v>1.71</v>
@@ -1773,28 +1773,28 @@
         <v>157.65</v>
       </c>
       <c r="M6">
-        <v>5.901196</v>
+        <v>7.376495</v>
       </c>
       <c r="N6">
-        <v>151.748804</v>
+        <v>150.273505</v>
       </c>
       <c r="O6">
-        <v>45.52464119999999</v>
+        <v>45.08205149999999</v>
       </c>
       <c r="P6">
-        <v>106.2241628</v>
+        <v>105.1914535</v>
       </c>
       <c r="Q6">
-        <v>176.3241628</v>
+        <v>175.2914535</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09059098365549859</v>
+        <v>0.09092503105118203</v>
       </c>
       <c r="T6">
-        <v>0.6165647495673705</v>
+        <v>0.6211630377060575</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.71492355109032</v>
+        <v>21.37193884087225</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08813927949862292</v>
+        <v>0.08790281468796722</v>
       </c>
       <c r="C7">
-        <v>2821.38933462053</v>
+        <v>2805.636137427606</v>
       </c>
       <c r="D7">
-        <v>2966.329334620531</v>
+        <v>2979.906137427606</v>
       </c>
       <c r="E7">
-        <v>-375.0500000000001</v>
+        <v>-345.72</v>
       </c>
       <c r="F7">
-        <v>146.65</v>
+        <v>175.98</v>
       </c>
       <c r="G7">
         <v>1.71</v>
@@ -1855,28 +1855,28 @@
         <v>157.65</v>
       </c>
       <c r="M7">
-        <v>7.376495</v>
+        <v>8.851794</v>
       </c>
       <c r="N7">
-        <v>150.273505</v>
+        <v>148.798206</v>
       </c>
       <c r="O7">
-        <v>45.08205149999999</v>
+        <v>44.63946179999999</v>
       </c>
       <c r="P7">
-        <v>105.1914535</v>
+        <v>104.1587442</v>
       </c>
       <c r="Q7">
-        <v>175.2914535</v>
+        <v>174.2587442</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09092503105118203</v>
+        <v>0.091266185838263</v>
       </c>
       <c r="T7">
-        <v>0.6211630377060575</v>
+        <v>0.6258591617625888</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.37193884087225</v>
+        <v>17.80994903406021</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08790281468796722</v>
+        <v>0.08766634987731153</v>
       </c>
       <c r="C8">
-        <v>2805.636137427606</v>
+        <v>2790.007792942434</v>
       </c>
       <c r="D8">
-        <v>2979.906137427606</v>
+        <v>2993.607792942434</v>
       </c>
       <c r="E8">
-        <v>-345.72</v>
+        <v>-316.3900000000001</v>
       </c>
       <c r="F8">
-        <v>175.98</v>
+        <v>205.31</v>
       </c>
       <c r="G8">
         <v>1.71</v>
@@ -1937,28 +1937,28 @@
         <v>157.65</v>
       </c>
       <c r="M8">
-        <v>8.851793999999998</v>
+        <v>10.327093</v>
       </c>
       <c r="N8">
-        <v>148.798206</v>
+        <v>147.322907</v>
       </c>
       <c r="O8">
-        <v>44.6394618</v>
+        <v>44.19687209999999</v>
       </c>
       <c r="P8">
-        <v>104.1587442</v>
+        <v>103.1260349</v>
       </c>
       <c r="Q8">
-        <v>174.2587442</v>
+        <v>173.2260349</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.091266185838263</v>
+        <v>0.09161467728743175</v>
       </c>
       <c r="T8">
-        <v>0.6258591617625888</v>
+        <v>0.6306562777343145</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.80994903406022</v>
+        <v>15.26567060062304</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08766634987731152</v>
+        <v>0.08742988506665583</v>
       </c>
       <c r="C9">
-        <v>2790.007792942435</v>
+        <v>2774.506031344581</v>
       </c>
       <c r="D9">
-        <v>2993.607792942435</v>
+        <v>3007.43603134458</v>
       </c>
       <c r="E9">
-        <v>-316.39</v>
+        <v>-287.0600000000001</v>
       </c>
       <c r="F9">
-        <v>205.31</v>
+        <v>234.64</v>
       </c>
       <c r="G9">
         <v>1.71</v>
@@ -2019,28 +2019,28 @@
         <v>157.65</v>
       </c>
       <c r="M9">
-        <v>10.327093</v>
+        <v>11.802392</v>
       </c>
       <c r="N9">
-        <v>147.322907</v>
+        <v>145.847608</v>
       </c>
       <c r="O9">
-        <v>44.19687209999999</v>
+        <v>43.75428239999999</v>
       </c>
       <c r="P9">
-        <v>103.1260349</v>
+        <v>102.0933256</v>
       </c>
       <c r="Q9">
-        <v>173.2260349</v>
+        <v>172.1933256</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09161467728743175</v>
+        <v>0.09197074463766938</v>
       </c>
       <c r="T9">
-        <v>0.6306562777343145</v>
+        <v>0.6355576788358603</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.26567060062304</v>
+        <v>13.35746177554516</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08742988506665583</v>
+        <v>0.08728792025600011</v>
       </c>
       <c r="C10">
-        <v>2774.506031344581</v>
+        <v>2753.539542015826</v>
       </c>
       <c r="D10">
-        <v>3007.43603134458</v>
+        <v>3015.799542015826</v>
       </c>
       <c r="E10">
-        <v>-287.0600000000001</v>
+        <v>-257.7300000000001</v>
       </c>
       <c r="F10">
-        <v>234.64</v>
+        <v>263.97</v>
       </c>
       <c r="G10">
         <v>1.71</v>
@@ -2101,45 +2101,45 @@
         <v>157.65</v>
       </c>
       <c r="M10">
-        <v>11.802392</v>
+        <v>13.673646</v>
       </c>
       <c r="N10">
-        <v>145.847608</v>
+        <v>143.976354</v>
       </c>
       <c r="O10">
-        <v>43.75428239999999</v>
+        <v>43.1929062</v>
       </c>
       <c r="P10">
-        <v>102.0933256</v>
+        <v>100.7834478</v>
       </c>
       <c r="Q10">
-        <v>172.1933256</v>
+        <v>170.8834478</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09197074463766938</v>
+        <v>0.09233463764395616</v>
       </c>
       <c r="T10">
-        <v>0.6355576788358603</v>
+        <v>0.6405668030385389</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.35746177554516</v>
+        <v>11.5294779461162</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08728792025600011</v>
+        <v>0.08706195544534441</v>
       </c>
       <c r="C11">
-        <v>2753.539542015826</v>
+        <v>2737.618080037993</v>
       </c>
       <c r="D11">
-        <v>3015.799542015826</v>
+        <v>3029.208080037993</v>
       </c>
       <c r="E11">
-        <v>-257.7300000000001</v>
+        <v>-228.4000000000001</v>
       </c>
       <c r="F11">
-        <v>263.97</v>
+        <v>293.3</v>
       </c>
       <c r="G11">
         <v>1.71</v>
@@ -2183,28 +2183,28 @@
         <v>157.65</v>
       </c>
       <c r="M11">
-        <v>13.673646</v>
+        <v>15.19294</v>
       </c>
       <c r="N11">
-        <v>143.976354</v>
+        <v>142.45706</v>
       </c>
       <c r="O11">
-        <v>43.1929062</v>
+        <v>42.737118</v>
       </c>
       <c r="P11">
-        <v>100.7834478</v>
+        <v>99.71994199999999</v>
       </c>
       <c r="Q11">
-        <v>170.8834478</v>
+        <v>169.819942</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09233463764395616</v>
+        <v>0.09270661716149378</v>
       </c>
       <c r="T11">
-        <v>0.6405668030385389</v>
+        <v>0.6456872411123881</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.5294779461162</v>
+        <v>10.37653015150458</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08706195544534441</v>
+        <v>0.08696689063468871</v>
       </c>
       <c r="C12">
-        <v>2737.618080037993</v>
+        <v>2713.964834996169</v>
       </c>
       <c r="D12">
-        <v>3029.208080037993</v>
+        <v>3034.884834996169</v>
       </c>
       <c r="E12">
-        <v>-228.4</v>
+        <v>-199.0700000000001</v>
       </c>
       <c r="F12">
-        <v>293.3</v>
+        <v>322.63</v>
       </c>
       <c r="G12">
         <v>1.71</v>
@@ -2265,45 +2265,45 @@
         <v>157.65</v>
       </c>
       <c r="M12">
-        <v>15.19294</v>
+        <v>17.260705</v>
       </c>
       <c r="N12">
-        <v>142.45706</v>
+        <v>140.389295</v>
       </c>
       <c r="O12">
-        <v>42.737118</v>
+        <v>42.11678849999999</v>
       </c>
       <c r="P12">
-        <v>99.71994199999999</v>
+        <v>98.27250649999999</v>
       </c>
       <c r="Q12">
-        <v>169.819942</v>
+        <v>168.3725065</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09270661716149378</v>
+        <v>0.09308695576931315</v>
       </c>
       <c r="T12">
-        <v>0.6456872411123881</v>
+        <v>0.6509227452103687</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.37653015150458</v>
+        <v>9.133462393337931</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08696689063468871</v>
+        <v>0.086752825824033</v>
       </c>
       <c r="C13">
-        <v>2713.964834996169</v>
+        <v>2697.49585114738</v>
       </c>
       <c r="D13">
-        <v>3034.884834996169</v>
+        <v>3047.74585114738</v>
       </c>
       <c r="E13">
-        <v>-199.0700000000001</v>
+        <v>-169.7400000000001</v>
       </c>
       <c r="F13">
-        <v>322.63</v>
+        <v>351.96</v>
       </c>
       <c r="G13">
         <v>1.71</v>
@@ -2347,28 +2347,28 @@
         <v>157.65</v>
       </c>
       <c r="M13">
-        <v>17.260705</v>
+        <v>18.82986</v>
       </c>
       <c r="N13">
-        <v>140.389295</v>
+        <v>138.82014</v>
       </c>
       <c r="O13">
-        <v>42.11678849999999</v>
+        <v>41.64604199999999</v>
       </c>
       <c r="P13">
-        <v>98.27250649999999</v>
+        <v>97.17409799999999</v>
       </c>
       <c r="Q13">
-        <v>168.3725065</v>
+        <v>167.274098</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09308695576931315</v>
+        <v>0.09347593843640115</v>
       </c>
       <c r="T13">
-        <v>0.6509227452103687</v>
+        <v>0.656277238037849</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.133462393337931</v>
+        <v>8.372340527226436</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.086752825824033</v>
+        <v>0.08653876101337729</v>
       </c>
       <c r="C14">
-        <v>2697.49585114738</v>
+        <v>2681.13633416342</v>
       </c>
       <c r="D14">
-        <v>3047.74585114738</v>
+        <v>3060.71633416342</v>
       </c>
       <c r="E14">
-        <v>-169.7400000000001</v>
+        <v>-140.41</v>
       </c>
       <c r="F14">
-        <v>351.96</v>
+        <v>381.29</v>
       </c>
       <c r="G14">
         <v>1.71</v>
@@ -2429,28 +2429,28 @@
         <v>157.65</v>
       </c>
       <c r="M14">
-        <v>18.82986</v>
+        <v>20.399015</v>
       </c>
       <c r="N14">
-        <v>138.82014</v>
+        <v>137.250985</v>
       </c>
       <c r="O14">
-        <v>41.64604199999999</v>
+        <v>41.1752955</v>
       </c>
       <c r="P14">
-        <v>97.17409799999999</v>
+        <v>96.07568949999998</v>
       </c>
       <c r="Q14">
-        <v>167.274098</v>
+        <v>166.1756895</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09347593843640115</v>
+        <v>0.09387386323376701</v>
       </c>
       <c r="T14">
-        <v>0.656277238037849</v>
+        <v>0.6617548226544666</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.372340527226436</v>
+        <v>7.728314332824402</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08653876101337729</v>
+        <v>0.0864030962027216</v>
       </c>
       <c r="C15">
-        <v>2681.13633416342</v>
+        <v>2660.08376075882</v>
       </c>
       <c r="D15">
-        <v>3060.71633416342</v>
+        <v>3068.993760758819</v>
       </c>
       <c r="E15">
-        <v>-140.41</v>
+        <v>-111.08</v>
       </c>
       <c r="F15">
-        <v>381.29</v>
+        <v>410.6200000000001</v>
       </c>
       <c r="G15">
         <v>1.71</v>
@@ -2511,45 +2511,45 @@
         <v>157.65</v>
       </c>
       <c r="M15">
-        <v>20.399015</v>
+        <v>22.29666600000001</v>
       </c>
       <c r="N15">
-        <v>137.250985</v>
+        <v>135.353334</v>
       </c>
       <c r="O15">
-        <v>41.1752955</v>
+        <v>40.60600019999999</v>
       </c>
       <c r="P15">
-        <v>96.07568949999998</v>
+        <v>94.74733379999998</v>
       </c>
       <c r="Q15">
-        <v>166.1756895</v>
+        <v>164.8473338</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09387386323376701</v>
+        <v>0.0942810420961879</v>
       </c>
       <c r="T15">
-        <v>0.6617548226544666</v>
+        <v>0.6673597929598429</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.728314332824402</v>
+        <v>7.070563823308827</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0864030962027216</v>
+        <v>0.08619463139206589</v>
       </c>
       <c r="C16">
-        <v>2660.08376075882</v>
+        <v>2643.560611156218</v>
       </c>
       <c r="D16">
-        <v>3068.993760758819</v>
+        <v>3081.800611156219</v>
       </c>
       <c r="E16">
-        <v>-111.08</v>
+        <v>-81.75</v>
       </c>
       <c r="F16">
-        <v>410.6200000000001</v>
+        <v>439.95</v>
       </c>
       <c r="G16">
         <v>1.71</v>
@@ -2593,28 +2593,28 @@
         <v>157.65</v>
       </c>
       <c r="M16">
-        <v>22.29666600000001</v>
+        <v>23.889285</v>
       </c>
       <c r="N16">
-        <v>135.353334</v>
+        <v>133.760715</v>
       </c>
       <c r="O16">
-        <v>40.60600019999999</v>
+        <v>40.12821449999999</v>
       </c>
       <c r="P16">
-        <v>94.74733379999998</v>
+        <v>93.63250049999999</v>
       </c>
       <c r="Q16">
-        <v>164.8473338</v>
+        <v>163.7325005</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0942810420961879</v>
+        <v>0.09469780163772458</v>
       </c>
       <c r="T16">
-        <v>0.6673597929598429</v>
+        <v>0.6730966449194634</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.070563823308827</v>
+        <v>6.599192901754906</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08619463139206589</v>
+        <v>0.08598616658141017</v>
       </c>
       <c r="C17">
-        <v>2643.560611156219</v>
+        <v>2627.144794921578</v>
       </c>
       <c r="D17">
-        <v>3081.800611156219</v>
+        <v>3094.714794921578</v>
       </c>
       <c r="E17">
-        <v>-81.75000000000006</v>
+        <v>-52.42000000000002</v>
       </c>
       <c r="F17">
-        <v>439.95</v>
+        <v>469.28</v>
       </c>
       <c r="G17">
         <v>1.71</v>
@@ -2675,28 +2675,28 @@
         <v>157.65</v>
       </c>
       <c r="M17">
-        <v>23.889285</v>
+        <v>25.481904</v>
       </c>
       <c r="N17">
-        <v>133.760715</v>
+        <v>132.168096</v>
       </c>
       <c r="O17">
-        <v>40.12821449999999</v>
+        <v>39.65042879999999</v>
       </c>
       <c r="P17">
-        <v>93.63250049999999</v>
+        <v>92.51766719999998</v>
       </c>
       <c r="Q17">
-        <v>163.7325005</v>
+        <v>162.6176672</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09469780163772458</v>
+        <v>0.09512448402548832</v>
       </c>
       <c r="T17">
-        <v>0.6730966449194634</v>
+        <v>0.678970088592408</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.599192901754907</v>
+        <v>6.186743345395224</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08598616658141017</v>
+        <v>0.08589670177075448</v>
       </c>
       <c r="C18">
-        <v>2627.144794921578</v>
+        <v>2603.390300802263</v>
       </c>
       <c r="D18">
-        <v>3094.714794921578</v>
+        <v>3100.290300802264</v>
       </c>
       <c r="E18">
-        <v>-52.42000000000002</v>
+        <v>-23.09000000000003</v>
       </c>
       <c r="F18">
-        <v>469.28</v>
+        <v>498.61</v>
       </c>
       <c r="G18">
         <v>1.71</v>
@@ -2757,45 +2757,45 @@
         <v>157.65</v>
       </c>
       <c r="M18">
-        <v>25.481904</v>
+        <v>27.573133</v>
       </c>
       <c r="N18">
-        <v>132.168096</v>
+        <v>130.076867</v>
       </c>
       <c r="O18">
-        <v>39.65042879999999</v>
+        <v>39.02306009999999</v>
       </c>
       <c r="P18">
-        <v>92.51766719999998</v>
+        <v>91.05380689999998</v>
       </c>
       <c r="Q18">
-        <v>162.6176672</v>
+        <v>161.1538069</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09512448402548832</v>
+        <v>0.09556144791657167</v>
       </c>
       <c r="T18">
-        <v>0.678970088592408</v>
+        <v>0.6849850610285563</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.186743345395224</v>
+        <v>5.717522198148465</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08589670177075448</v>
+        <v>0.08569523696009876</v>
       </c>
       <c r="C19">
-        <v>2603.390300802263</v>
+        <v>2586.68957815154</v>
       </c>
       <c r="D19">
-        <v>3100.290300802264</v>
+        <v>3112.91957815154</v>
       </c>
       <c r="E19">
-        <v>-23.09000000000003</v>
+        <v>6.240000000000009</v>
       </c>
       <c r="F19">
-        <v>498.61</v>
+        <v>527.9400000000001</v>
       </c>
       <c r="G19">
         <v>1.71</v>
@@ -2839,28 +2839,28 @@
         <v>157.65</v>
       </c>
       <c r="M19">
-        <v>27.573133</v>
+        <v>29.195082</v>
       </c>
       <c r="N19">
-        <v>130.076867</v>
+        <v>128.454918</v>
       </c>
       <c r="O19">
-        <v>39.02306009999999</v>
+        <v>38.53647539999999</v>
       </c>
       <c r="P19">
-        <v>91.05380689999998</v>
+        <v>89.91844259999998</v>
       </c>
       <c r="Q19">
-        <v>161.1538069</v>
+        <v>160.0184426</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09556144791657167</v>
+        <v>0.09600906946353509</v>
       </c>
       <c r="T19">
-        <v>0.6849850610285563</v>
+        <v>0.6911467401094885</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.717522198148465</v>
+        <v>5.399882076029105</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08569523696009877</v>
+        <v>0.08549377214944308</v>
       </c>
       <c r="C20">
-        <v>2586.689578151539</v>
+        <v>2570.092169073873</v>
       </c>
       <c r="D20">
-        <v>3112.919578151539</v>
+        <v>3125.652169073873</v>
       </c>
       <c r="E20">
-        <v>6.239999999999895</v>
+        <v>35.56999999999994</v>
       </c>
       <c r="F20">
-        <v>527.9399999999999</v>
+        <v>557.27</v>
       </c>
       <c r="G20">
         <v>1.71</v>
@@ -2921,28 +2921,28 @@
         <v>157.65</v>
       </c>
       <c r="M20">
-        <v>29.195082</v>
+        <v>30.817031</v>
       </c>
       <c r="N20">
-        <v>128.454918</v>
+        <v>126.832969</v>
       </c>
       <c r="O20">
-        <v>38.53647539999999</v>
+        <v>38.04989069999999</v>
       </c>
       <c r="P20">
-        <v>89.91844259999998</v>
+        <v>88.78307829999999</v>
       </c>
       <c r="Q20">
-        <v>160.0184426</v>
+        <v>158.8830783</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09600906946353509</v>
+        <v>0.09646774339437417</v>
       </c>
       <c r="T20">
-        <v>0.6911467401094885</v>
+        <v>0.6974605594146414</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.399882076029106</v>
+        <v>5.1156777562381</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08549377214944308</v>
+        <v>0.08529230733878737</v>
       </c>
       <c r="C21">
-        <v>2570.092169073873</v>
+        <v>2553.599346508095</v>
       </c>
       <c r="D21">
-        <v>3125.652169073873</v>
+        <v>3138.489346508095</v>
       </c>
       <c r="E21">
-        <v>35.56999999999994</v>
+        <v>64.89999999999998</v>
       </c>
       <c r="F21">
-        <v>557.27</v>
+        <v>586.6</v>
       </c>
       <c r="G21">
         <v>1.71</v>
@@ -3003,28 +3003,28 @@
         <v>157.65</v>
       </c>
       <c r="M21">
-        <v>30.817031</v>
+        <v>32.43898</v>
       </c>
       <c r="N21">
-        <v>126.832969</v>
+        <v>125.21102</v>
       </c>
       <c r="O21">
-        <v>38.04989069999999</v>
+        <v>37.56330599999999</v>
       </c>
       <c r="P21">
-        <v>88.78307829999999</v>
+        <v>87.64771399999998</v>
       </c>
       <c r="Q21">
-        <v>158.8830783</v>
+        <v>157.747714</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09646774339437417</v>
+        <v>0.0969378841734842</v>
       </c>
       <c r="T21">
-        <v>0.6974605594146414</v>
+        <v>0.7039322242024231</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.1156777562381</v>
+        <v>4.859893868426195</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08529230733878737</v>
+        <v>0.08509084252813168</v>
       </c>
       <c r="C22">
-        <v>2553.599346508095</v>
+        <v>2537.212404391312</v>
       </c>
       <c r="D22">
-        <v>3138.489346508095</v>
+        <v>3151.432404391312</v>
       </c>
       <c r="E22">
-        <v>64.89999999999998</v>
+        <v>94.23000000000002</v>
       </c>
       <c r="F22">
-        <v>586.6</v>
+        <v>615.9300000000001</v>
       </c>
       <c r="G22">
         <v>1.71</v>
@@ -3085,28 +3085,28 @@
         <v>157.65</v>
       </c>
       <c r="M22">
-        <v>32.43898</v>
+        <v>34.060929</v>
       </c>
       <c r="N22">
-        <v>125.21102</v>
+        <v>123.589071</v>
       </c>
       <c r="O22">
-        <v>37.56330599999999</v>
+        <v>37.07672129999999</v>
       </c>
       <c r="P22">
-        <v>87.64771399999998</v>
+        <v>86.51234969999999</v>
       </c>
       <c r="Q22">
-        <v>157.747714</v>
+        <v>156.6123497</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0969378841734842</v>
+        <v>0.09741992725079958</v>
       </c>
       <c r="T22">
-        <v>0.7039322242024231</v>
+        <v>0.7105677286050853</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.859893868426195</v>
+        <v>4.628470350882091</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08509084252813166</v>
+        <v>0.08527437771747597</v>
       </c>
       <c r="C23">
-        <v>2537.212404391313</v>
+        <v>2496.08691929619</v>
       </c>
       <c r="D23">
-        <v>3151.432404391313</v>
+        <v>3139.63691929619</v>
       </c>
       <c r="E23">
-        <v>94.2299999999999</v>
+        <v>123.5599999999999</v>
       </c>
       <c r="F23">
-        <v>615.9299999999999</v>
+        <v>645.26</v>
       </c>
       <c r="G23">
         <v>1.71</v>
@@ -3167,45 +3167,45 @@
         <v>157.65</v>
       </c>
       <c r="M23">
-        <v>34.060929</v>
+        <v>37.296028</v>
       </c>
       <c r="N23">
-        <v>123.589071</v>
+        <v>120.353972</v>
       </c>
       <c r="O23">
-        <v>37.07672129999999</v>
+        <v>36.10619159999999</v>
       </c>
       <c r="P23">
-        <v>86.51234969999999</v>
+        <v>84.24778039999998</v>
       </c>
       <c r="Q23">
-        <v>156.6123497</v>
+        <v>154.3477804</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09741992725079957</v>
+        <v>0.09791433040702047</v>
       </c>
       <c r="T23">
-        <v>0.7105677286050852</v>
+        <v>0.7173733741462773</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.628470350882091</v>
+        <v>4.226991678577676</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08527437771747597</v>
+        <v>0.08509041290682025</v>
       </c>
       <c r="C24">
-        <v>2496.08691929619</v>
+        <v>2478.580119377516</v>
       </c>
       <c r="D24">
-        <v>3139.63691929619</v>
+        <v>3151.460119377516</v>
       </c>
       <c r="E24">
-        <v>123.5599999999999</v>
+        <v>152.89</v>
       </c>
       <c r="F24">
-        <v>645.26</v>
+        <v>674.59</v>
       </c>
       <c r="G24">
         <v>1.71</v>
@@ -3249,28 +3249,28 @@
         <v>157.65</v>
       </c>
       <c r="M24">
-        <v>37.296028</v>
+        <v>38.991302</v>
       </c>
       <c r="N24">
-        <v>120.353972</v>
+        <v>118.658698</v>
       </c>
       <c r="O24">
-        <v>36.10619159999999</v>
+        <v>35.59760939999999</v>
       </c>
       <c r="P24">
-        <v>84.24778039999998</v>
+        <v>83.06108859999998</v>
       </c>
       <c r="Q24">
-        <v>154.3477804</v>
+        <v>153.1610886</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09791433040702047</v>
+        <v>0.09842157520366265</v>
       </c>
       <c r="T24">
-        <v>0.7173733741462773</v>
+        <v>0.7243557897015261</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.226991678577676</v>
+        <v>4.043209431682993</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08509041290682025</v>
+        <v>0.08549444809616455</v>
       </c>
       <c r="C25">
-        <v>2478.580119377516</v>
+        <v>2423.399275045163</v>
       </c>
       <c r="D25">
-        <v>3151.460119377516</v>
+        <v>3125.609275045163</v>
       </c>
       <c r="E25">
-        <v>152.89</v>
+        <v>182.22</v>
       </c>
       <c r="F25">
-        <v>674.59</v>
+        <v>703.9200000000001</v>
       </c>
       <c r="G25">
         <v>1.71</v>
@@ -3331,45 +3331,45 @@
         <v>157.65</v>
       </c>
       <c r="M25">
-        <v>38.991302</v>
+        <v>43.150296</v>
       </c>
       <c r="N25">
-        <v>118.658698</v>
+        <v>114.499704</v>
       </c>
       <c r="O25">
-        <v>35.59760939999999</v>
+        <v>34.34991119999999</v>
       </c>
       <c r="P25">
-        <v>83.06108859999998</v>
+        <v>80.14979279999999</v>
       </c>
       <c r="Q25">
-        <v>153.1610886</v>
+        <v>150.2497928</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09842157520366265</v>
+        <v>0.09894216854758493</v>
       </c>
       <c r="T25">
-        <v>0.7243557897015261</v>
+        <v>0.7315219530345449</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.043209431682993</v>
+        <v>3.653509120771732</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08549444809616455</v>
+        <v>0.08533498328550884</v>
       </c>
       <c r="C26">
-        <v>2423.399275045163</v>
+        <v>2404.22127434708</v>
       </c>
       <c r="D26">
-        <v>3125.609275045163</v>
+        <v>3135.76127434708</v>
       </c>
       <c r="E26">
-        <v>182.2199999999999</v>
+        <v>211.55</v>
       </c>
       <c r="F26">
-        <v>703.92</v>
+        <v>733.25</v>
       </c>
       <c r="G26">
         <v>1.71</v>
@@ -3413,28 +3413,28 @@
         <v>157.65</v>
       </c>
       <c r="M26">
-        <v>43.150296</v>
+        <v>44.948225</v>
       </c>
       <c r="N26">
-        <v>114.499704</v>
+        <v>112.701775</v>
       </c>
       <c r="O26">
-        <v>34.34991119999999</v>
+        <v>33.81053249999999</v>
       </c>
       <c r="P26">
-        <v>80.14979279999999</v>
+        <v>78.89124249999998</v>
       </c>
       <c r="Q26">
-        <v>150.2497928</v>
+        <v>148.9912425</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09894216854758493</v>
+        <v>0.09947664438067846</v>
       </c>
       <c r="T26">
-        <v>0.7315219530345449</v>
+        <v>0.7388792140564441</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.653509120771732</v>
+        <v>3.507368755940862</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08533498328550884</v>
+        <v>0.08568511847485313</v>
       </c>
       <c r="C27">
-        <v>2404.22127434708</v>
+        <v>2352.686592487027</v>
       </c>
       <c r="D27">
-        <v>3135.76127434708</v>
+        <v>3113.556592487027</v>
       </c>
       <c r="E27">
-        <v>211.55</v>
+        <v>240.88</v>
       </c>
       <c r="F27">
-        <v>733.25</v>
+        <v>762.58</v>
       </c>
       <c r="G27">
         <v>1.71</v>
@@ -3495,45 +3495,45 @@
         <v>157.65</v>
       </c>
       <c r="M27">
-        <v>44.948225</v>
+        <v>48.88137800000001</v>
       </c>
       <c r="N27">
-        <v>112.701775</v>
+        <v>108.768622</v>
       </c>
       <c r="O27">
-        <v>33.81053249999999</v>
+        <v>32.63058659999999</v>
       </c>
       <c r="P27">
-        <v>78.89124249999998</v>
+        <v>76.13803539999998</v>
       </c>
       <c r="Q27">
-        <v>148.9912425</v>
+        <v>146.2380354</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09947664438067846</v>
+        <v>0.1000255655065583</v>
       </c>
       <c r="T27">
-        <v>0.7388792140564441</v>
+        <v>0.7464353199708269</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.507368755940862</v>
+        <v>3.225154577270713</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08568511847485313</v>
+        <v>0.08554525366419743</v>
       </c>
       <c r="C28">
-        <v>2352.686592487027</v>
+        <v>2332.188636440542</v>
       </c>
       <c r="D28">
-        <v>3113.556592487027</v>
+        <v>3122.388636440542</v>
       </c>
       <c r="E28">
-        <v>240.88</v>
+        <v>270.21</v>
       </c>
       <c r="F28">
-        <v>762.58</v>
+        <v>791.9100000000001</v>
       </c>
       <c r="G28">
         <v>1.71</v>
@@ -3577,28 +3577,28 @@
         <v>157.65</v>
       </c>
       <c r="M28">
-        <v>48.88137800000001</v>
+        <v>50.76143100000001</v>
       </c>
       <c r="N28">
-        <v>108.768622</v>
+        <v>106.888569</v>
       </c>
       <c r="O28">
-        <v>32.63058659999999</v>
+        <v>32.06657069999999</v>
       </c>
       <c r="P28">
-        <v>76.13803539999998</v>
+        <v>74.82199829999998</v>
       </c>
       <c r="Q28">
-        <v>146.2380354</v>
+        <v>144.9219983</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1000255655065583</v>
+        <v>0.1005895255673938</v>
       </c>
       <c r="T28">
-        <v>0.7464353199708269</v>
+        <v>0.7541984424856041</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.225154577270713</v>
+        <v>3.105704407742168</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08554525366419743</v>
+        <v>0.08693418885354173</v>
       </c>
       <c r="C29">
-        <v>2332.188636440542</v>
+        <v>2217.312529558155</v>
       </c>
       <c r="D29">
-        <v>3122.388636440542</v>
+        <v>3036.842529558156</v>
       </c>
       <c r="E29">
-        <v>270.21</v>
+        <v>299.5400000000001</v>
       </c>
       <c r="F29">
-        <v>791.9100000000001</v>
+        <v>821.2400000000001</v>
       </c>
       <c r="G29">
         <v>1.71</v>
@@ -3659,45 +3659,45 @@
         <v>157.65</v>
       </c>
       <c r="M29">
-        <v>50.76143100000001</v>
+        <v>59.04715600000002</v>
       </c>
       <c r="N29">
-        <v>106.888569</v>
+        <v>98.60284399999996</v>
       </c>
       <c r="O29">
-        <v>32.06657069999999</v>
+        <v>29.58085319999999</v>
       </c>
       <c r="P29">
-        <v>74.82199829999998</v>
+        <v>69.02199079999997</v>
       </c>
       <c r="Q29">
-        <v>144.9219983</v>
+        <v>139.1219908</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1005895255673938</v>
+        <v>0.1011691511854746</v>
       </c>
       <c r="T29">
-        <v>0.7541984424856041</v>
+        <v>0.7621772072924581</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.105704407742168</v>
+        <v>2.669899969441372</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08693418885354173</v>
+        <v>0.08684892404288602</v>
       </c>
       <c r="C30">
-        <v>2217.312529558155</v>
+        <v>2193.098811541152</v>
       </c>
       <c r="D30">
-        <v>3036.842529558156</v>
+        <v>3041.958811541152</v>
       </c>
       <c r="E30">
-        <v>299.5400000000001</v>
+        <v>328.87</v>
       </c>
       <c r="F30">
-        <v>821.2400000000001</v>
+        <v>850.5700000000001</v>
       </c>
       <c r="G30">
         <v>1.71</v>
@@ -3741,28 +3741,28 @@
         <v>157.65</v>
       </c>
       <c r="M30">
-        <v>59.04715600000002</v>
+        <v>61.15598300000001</v>
       </c>
       <c r="N30">
-        <v>98.60284399999996</v>
+        <v>96.49401699999997</v>
       </c>
       <c r="O30">
-        <v>29.58085319999999</v>
+        <v>28.94820509999999</v>
       </c>
       <c r="P30">
-        <v>69.02199079999997</v>
+        <v>67.54581189999999</v>
       </c>
       <c r="Q30">
-        <v>139.1219908</v>
+        <v>137.6458119</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1011691511854746</v>
+        <v>0.101765104285755</v>
       </c>
       <c r="T30">
-        <v>0.7621772072924581</v>
+        <v>0.7703807260375335</v>
       </c>
       <c r="U30">
         <v>0.07190000000000001</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.669899969441372</v>
+        <v>2.577834453253739</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08684892404288602</v>
+        <v>0.08758265923223031</v>
       </c>
       <c r="C31">
-        <v>2193.098811541152</v>
+        <v>2120.297380101284</v>
       </c>
       <c r="D31">
-        <v>3041.958811541152</v>
+        <v>2998.487380101285</v>
       </c>
       <c r="E31">
-        <v>328.8699999999999</v>
+        <v>358.1999999999999</v>
       </c>
       <c r="F31">
-        <v>850.5699999999999</v>
+        <v>879.9</v>
       </c>
       <c r="G31">
         <v>1.71</v>
@@ -3823,45 +3823,45 @@
         <v>157.65</v>
       </c>
       <c r="M31">
-        <v>61.155983</v>
+        <v>66.69642</v>
       </c>
       <c r="N31">
-        <v>96.49401699999999</v>
+        <v>90.95357999999997</v>
       </c>
       <c r="O31">
-        <v>28.9482051</v>
+        <v>27.28607399999999</v>
       </c>
       <c r="P31">
-        <v>67.54581189999999</v>
+        <v>63.66750599999998</v>
       </c>
       <c r="Q31">
-        <v>137.6458119</v>
+        <v>133.767506</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.101765104285755</v>
+        <v>0.1023780846174719</v>
       </c>
       <c r="T31">
-        <v>0.7703807260375335</v>
+        <v>0.7788186310324681</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.57783445325374</v>
+        <v>2.363695082884508</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08758265923223031</v>
+        <v>0.08752469442157462</v>
       </c>
       <c r="C32">
-        <v>2120.297380101284</v>
+        <v>2094.356356039765</v>
       </c>
       <c r="D32">
-        <v>2998.487380101285</v>
+        <v>3001.876356039765</v>
       </c>
       <c r="E32">
-        <v>358.1999999999999</v>
+        <v>387.53</v>
       </c>
       <c r="F32">
-        <v>879.9</v>
+        <v>909.23</v>
       </c>
       <c r="G32">
         <v>1.71</v>
@@ -3905,28 +3905,28 @@
         <v>157.65</v>
       </c>
       <c r="M32">
-        <v>66.69642</v>
+        <v>68.919634</v>
       </c>
       <c r="N32">
-        <v>90.95357999999997</v>
+        <v>88.73036599999998</v>
       </c>
       <c r="O32">
-        <v>27.28607399999999</v>
+        <v>26.61910979999999</v>
       </c>
       <c r="P32">
-        <v>63.66750599999998</v>
+        <v>62.11125619999999</v>
       </c>
       <c r="Q32">
-        <v>133.767506</v>
+        <v>132.2112562</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1023780846174719</v>
+        <v>0.1030088324950357</v>
       </c>
       <c r="T32">
-        <v>0.7788186310324681</v>
+        <v>0.7875011129837776</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.363695082884508</v>
+        <v>2.287446854404363</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08752469442157462</v>
+        <v>0.08746672961091891</v>
       </c>
       <c r="C33">
-        <v>2094.356356039765</v>
+        <v>2068.423001280795</v>
       </c>
       <c r="D33">
-        <v>3001.876356039765</v>
+        <v>3005.273001280795</v>
       </c>
       <c r="E33">
-        <v>387.53</v>
+        <v>416.86</v>
       </c>
       <c r="F33">
-        <v>909.23</v>
+        <v>938.5600000000001</v>
       </c>
       <c r="G33">
         <v>1.71</v>
@@ -3987,28 +3987,28 @@
         <v>157.65</v>
       </c>
       <c r="M33">
-        <v>68.919634</v>
+        <v>71.14284800000001</v>
       </c>
       <c r="N33">
-        <v>88.73036599999998</v>
+        <v>86.50715199999996</v>
       </c>
       <c r="O33">
-        <v>26.61910979999999</v>
+        <v>25.95214559999999</v>
       </c>
       <c r="P33">
-        <v>62.11125619999999</v>
+        <v>60.55500639999998</v>
       </c>
       <c r="Q33">
-        <v>132.2112562</v>
+        <v>130.6550064</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1030088324950357</v>
+        <v>0.1036581317807631</v>
       </c>
       <c r="T33">
-        <v>0.7875011129837776</v>
+        <v>0.7964389620513022</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.287446854404363</v>
+        <v>2.215964140204226</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08746672961091891</v>
+        <v>0.08740876480026322</v>
       </c>
       <c r="C34">
-        <v>2068.423001280795</v>
+        <v>2042.497341887479</v>
       </c>
       <c r="D34">
-        <v>3005.273001280795</v>
+        <v>3008.677341887479</v>
       </c>
       <c r="E34">
-        <v>416.86</v>
+        <v>446.1900000000001</v>
       </c>
       <c r="F34">
-        <v>938.5600000000001</v>
+        <v>967.8900000000001</v>
       </c>
       <c r="G34">
         <v>1.71</v>
@@ -4069,28 +4069,28 @@
         <v>157.65</v>
       </c>
       <c r="M34">
-        <v>71.14284800000001</v>
+        <v>73.36606200000001</v>
       </c>
       <c r="N34">
-        <v>86.50715199999996</v>
+        <v>84.28393799999996</v>
       </c>
       <c r="O34">
-        <v>25.95214559999999</v>
+        <v>25.28518139999999</v>
       </c>
       <c r="P34">
-        <v>60.55500639999998</v>
+        <v>58.99875659999998</v>
       </c>
       <c r="Q34">
-        <v>130.6550064</v>
+        <v>129.0987566</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1036581317807631</v>
+        <v>0.1043268131347212</v>
       </c>
       <c r="T34">
-        <v>0.7964389620513022</v>
+        <v>0.8056436125835291</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.215964140204226</v>
+        <v>2.148813711713189</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08740876480026322</v>
+        <v>0.0873507999896075</v>
       </c>
       <c r="C35">
-        <v>2042.497341887479</v>
+        <v>2016.579404041159</v>
       </c>
       <c r="D35">
-        <v>3008.677341887479</v>
+        <v>3012.089404041159</v>
       </c>
       <c r="E35">
-        <v>446.1900000000001</v>
+        <v>475.52</v>
       </c>
       <c r="F35">
-        <v>967.8900000000001</v>
+        <v>997.22</v>
       </c>
       <c r="G35">
         <v>1.71</v>
@@ -4151,28 +4151,28 @@
         <v>157.65</v>
       </c>
       <c r="M35">
-        <v>73.36606200000001</v>
+        <v>75.58927600000001</v>
       </c>
       <c r="N35">
-        <v>84.28393799999996</v>
+        <v>82.06072399999996</v>
       </c>
       <c r="O35">
-        <v>25.28518139999999</v>
+        <v>24.61821719999999</v>
       </c>
       <c r="P35">
-        <v>58.99875659999998</v>
+        <v>57.44250679999998</v>
       </c>
       <c r="Q35">
-        <v>129.0987566</v>
+        <v>127.5425068</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1043268131347212</v>
+        <v>0.1050157575600114</v>
       </c>
       <c r="T35">
-        <v>0.8056436125835291</v>
+        <v>0.8151271919197626</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.148813711713189</v>
+        <v>2.085613308427507</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0873507999896075</v>
+        <v>0.0872928351789518</v>
       </c>
       <c r="C36">
-        <v>2016.579404041159</v>
+        <v>1990.669214042071</v>
       </c>
       <c r="D36">
-        <v>3012.089404041159</v>
+        <v>3015.509214042071</v>
       </c>
       <c r="E36">
-        <v>475.52</v>
+        <v>504.8500000000001</v>
       </c>
       <c r="F36">
-        <v>997.22</v>
+        <v>1026.55</v>
       </c>
       <c r="G36">
         <v>1.71</v>
@@ -4233,28 +4233,28 @@
         <v>157.65</v>
       </c>
       <c r="M36">
-        <v>75.58927600000001</v>
+        <v>77.81249000000003</v>
       </c>
       <c r="N36">
-        <v>82.06072399999996</v>
+        <v>79.83750999999995</v>
       </c>
       <c r="O36">
-        <v>24.61821719999999</v>
+        <v>23.95125299999998</v>
       </c>
       <c r="P36">
-        <v>57.44250679999998</v>
+        <v>55.88625699999997</v>
       </c>
       <c r="Q36">
-        <v>127.5425068</v>
+        <v>125.986257</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1050157575600114</v>
+        <v>0.1057259002753105</v>
       </c>
       <c r="T36">
-        <v>0.8151271919197626</v>
+        <v>0.8249025736971112</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.085613308427507</v>
+        <v>2.026024356758149</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0872928351789518</v>
+        <v>0.09081327036829609</v>
       </c>
       <c r="C37">
-        <v>1990.669214042071</v>
+        <v>1766.817866378741</v>
       </c>
       <c r="D37">
-        <v>3015.509214042071</v>
+        <v>2820.987866378741</v>
       </c>
       <c r="E37">
-        <v>504.8500000000001</v>
+        <v>534.1800000000001</v>
       </c>
       <c r="F37">
-        <v>1026.55</v>
+        <v>1055.88</v>
       </c>
       <c r="G37">
         <v>1.71</v>
@@ -4315,45 +4315,45 @@
         <v>157.65</v>
       </c>
       <c r="M37">
-        <v>77.81249000000003</v>
+        <v>95.0292</v>
       </c>
       <c r="N37">
-        <v>79.83750999999995</v>
+        <v>62.62079999999997</v>
       </c>
       <c r="O37">
-        <v>23.95125299999998</v>
+        <v>18.78623999999999</v>
       </c>
       <c r="P37">
-        <v>55.88625699999997</v>
+        <v>43.83455999999998</v>
       </c>
       <c r="Q37">
-        <v>125.986257</v>
+        <v>113.93456</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1057259002753105</v>
+        <v>0.1064582349504627</v>
       </c>
       <c r="T37">
-        <v>0.8249025736971112</v>
+        <v>0.8349834361550018</v>
       </c>
       <c r="U37">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.026024356758149</v>
+        <v>1.658963771135609</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09081327036829609</v>
+        <v>0.09085470555764039</v>
       </c>
       <c r="C38">
-        <v>1766.817866378741</v>
+        <v>1735.347681982264</v>
       </c>
       <c r="D38">
-        <v>2820.987866378741</v>
+        <v>2818.847681982264</v>
       </c>
       <c r="E38">
-        <v>534.1799999999998</v>
+        <v>563.51</v>
       </c>
       <c r="F38">
-        <v>1055.88</v>
+        <v>1085.21</v>
       </c>
       <c r="G38">
         <v>1.71</v>
@@ -4397,28 +4397,28 @@
         <v>157.65</v>
       </c>
       <c r="M38">
-        <v>95.02919999999999</v>
+        <v>97.66889999999999</v>
       </c>
       <c r="N38">
-        <v>62.62079999999999</v>
+        <v>59.98109999999998</v>
       </c>
       <c r="O38">
-        <v>18.78624</v>
+        <v>17.99432999999999</v>
       </c>
       <c r="P38">
-        <v>43.83456</v>
+        <v>41.98676999999999</v>
       </c>
       <c r="Q38">
-        <v>113.93456</v>
+        <v>112.08677</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1064582349504627</v>
+        <v>0.1072138183454609</v>
       </c>
       <c r="T38">
-        <v>0.8349834361550018</v>
+        <v>0.845384325992508</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.658963771135609</v>
+        <v>1.614126912456268</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09085470555764039</v>
+        <v>0.0908961407469847</v>
       </c>
       <c r="C39">
-        <v>1735.347681982264</v>
+        <v>1703.880742489431</v>
       </c>
       <c r="D39">
-        <v>2818.847681982264</v>
+        <v>2816.710742489431</v>
       </c>
       <c r="E39">
-        <v>563.51</v>
+        <v>592.8399999999999</v>
       </c>
       <c r="F39">
-        <v>1085.21</v>
+        <v>1114.54</v>
       </c>
       <c r="G39">
         <v>1.71</v>
@@ -4479,28 +4479,28 @@
         <v>157.65</v>
       </c>
       <c r="M39">
-        <v>97.66889999999999</v>
+        <v>100.3086</v>
       </c>
       <c r="N39">
-        <v>59.98109999999998</v>
+        <v>57.34139999999998</v>
       </c>
       <c r="O39">
-        <v>17.99432999999999</v>
+        <v>17.20241999999999</v>
       </c>
       <c r="P39">
-        <v>41.98676999999999</v>
+        <v>40.13897999999999</v>
       </c>
       <c r="Q39">
-        <v>112.08677</v>
+        <v>110.23898</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1072138183454609</v>
+        <v>0.1079937753983624</v>
       </c>
       <c r="T39">
-        <v>0.845384325992508</v>
+        <v>0.8561207284054178</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.614126912456268</v>
+        <v>1.571649888444261</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0908961407469847</v>
+        <v>0.09093757593632898</v>
       </c>
       <c r="C40">
-        <v>1703.880742489431</v>
+        <v>1672.41704052605</v>
       </c>
       <c r="D40">
-        <v>2816.710742489431</v>
+        <v>2814.57704052605</v>
       </c>
       <c r="E40">
-        <v>592.8399999999999</v>
+        <v>622.1700000000001</v>
       </c>
       <c r="F40">
-        <v>1114.54</v>
+        <v>1143.87</v>
       </c>
       <c r="G40">
         <v>1.71</v>
@@ -4561,28 +4561,28 @@
         <v>157.65</v>
       </c>
       <c r="M40">
-        <v>100.3086</v>
+        <v>102.9483</v>
       </c>
       <c r="N40">
-        <v>57.34139999999998</v>
+        <v>54.70169999999997</v>
       </c>
       <c r="O40">
-        <v>17.20241999999999</v>
+        <v>16.41050999999999</v>
       </c>
       <c r="P40">
-        <v>40.13897999999999</v>
+        <v>38.29118999999999</v>
       </c>
       <c r="Q40">
-        <v>110.23898</v>
+        <v>108.39119</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1079937753983624</v>
+        <v>0.1087993048136541</v>
       </c>
       <c r="T40">
-        <v>0.8561207284054178</v>
+        <v>0.8672091440121933</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.571649888444261</v>
+        <v>1.531351173355946</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09093757593632898</v>
+        <v>0.1088158801804681</v>
       </c>
       <c r="C41">
-        <v>1672.41704052605</v>
+        <v>949.7573296314592</v>
       </c>
       <c r="D41">
-        <v>2814.57704052605</v>
+        <v>2121.247329631459</v>
       </c>
       <c r="E41">
-        <v>622.1700000000001</v>
+        <v>651.5</v>
       </c>
       <c r="F41">
-        <v>1143.87</v>
+        <v>1173.2</v>
       </c>
       <c r="G41">
         <v>1.71</v>
@@ -4643,45 +4643,45 @@
         <v>157.65</v>
       </c>
       <c r="M41">
-        <v>102.9483</v>
+        <v>172.22576</v>
       </c>
       <c r="N41">
-        <v>54.70169999999997</v>
+        <v>-14.57576000000006</v>
       </c>
       <c r="O41">
-        <v>16.41050999999999</v>
+        <v>-4.372728000000017</v>
       </c>
       <c r="P41">
-        <v>38.29118999999999</v>
+        <v>-10.20303200000004</v>
       </c>
       <c r="Q41">
-        <v>108.39119</v>
+        <v>59.89696799999995</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1087993048136541</v>
+        <v>0.1103683467265104</v>
       </c>
       <c r="T41">
-        <v>0.8672091440121933</v>
+        <v>0.8888075965378546</v>
       </c>
       <c r="U41">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.3</v>
+        <v>0.2746104880013303</v>
       </c>
       <c r="W41">
-        <v>0.063</v>
+        <v>0.1064871803614047</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.531351173355946</v>
+        <v>0.9153682933377675</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1088158801804681</v>
+        <v>0.1098258801804681</v>
       </c>
       <c r="C42">
-        <v>949.7573296314592</v>
+        <v>891.3127212606091</v>
       </c>
       <c r="D42">
-        <v>2121.247329631459</v>
+        <v>2092.132721260609</v>
       </c>
       <c r="E42">
-        <v>651.5</v>
+        <v>680.8300000000002</v>
       </c>
       <c r="F42">
-        <v>1173.2</v>
+        <v>1202.53</v>
       </c>
       <c r="G42">
         <v>1.71</v>
@@ -4725,37 +4725,37 @@
         <v>157.65</v>
       </c>
       <c r="M42">
-        <v>172.22576</v>
+        <v>176.531404</v>
       </c>
       <c r="N42">
-        <v>-14.57576000000006</v>
+        <v>-18.88140400000006</v>
       </c>
       <c r="O42">
-        <v>-4.372728000000017</v>
+        <v>-5.664421200000018</v>
       </c>
       <c r="P42">
-        <v>-10.20303200000004</v>
+        <v>-13.21698280000004</v>
       </c>
       <c r="Q42">
-        <v>59.89696799999995</v>
+        <v>56.88301719999995</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1103683467265104</v>
+        <v>0.1114627254845868</v>
       </c>
       <c r="T42">
-        <v>0.8888075965378546</v>
+        <v>0.9038721320723945</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2746104880013303</v>
+        <v>0.26791267122081</v>
       </c>
       <c r="W42">
-        <v>0.1064871803614047</v>
+        <v>0.1074704198647851</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.9153682933377675</v>
+        <v>0.8930422374027001</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1098258801804681</v>
+        <v>0.1108358801804681</v>
       </c>
       <c r="C43">
-        <v>891.3127212606091</v>
+        <v>833.6565014913308</v>
       </c>
       <c r="D43">
-        <v>2092.132721260609</v>
+        <v>2063.806501491331</v>
       </c>
       <c r="E43">
-        <v>680.8300000000002</v>
+        <v>710.1600000000001</v>
       </c>
       <c r="F43">
-        <v>1202.53</v>
+        <v>1231.86</v>
       </c>
       <c r="G43">
         <v>1.71</v>
@@ -4807,37 +4807,37 @@
         <v>157.65</v>
       </c>
       <c r="M43">
-        <v>176.531404</v>
+        <v>180.837048</v>
       </c>
       <c r="N43">
-        <v>-18.88140400000006</v>
+        <v>-23.18704800000006</v>
       </c>
       <c r="O43">
-        <v>-5.664421200000018</v>
+        <v>-6.956114400000018</v>
       </c>
       <c r="P43">
-        <v>-13.21698280000004</v>
+        <v>-16.23093360000004</v>
       </c>
       <c r="Q43">
-        <v>56.88301719999995</v>
+        <v>53.86906639999995</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1114627254845868</v>
+        <v>0.1125948414412176</v>
       </c>
       <c r="T43">
-        <v>0.9038721320723945</v>
+        <v>0.9194561343495047</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.26791267122081</v>
+        <v>0.261533798096505</v>
       </c>
       <c r="W43">
-        <v>0.1074704198647851</v>
+        <v>0.1084068384394331</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8930422374027001</v>
+        <v>0.87177932698835</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1108358801804681</v>
+        <v>0.1118458801804681</v>
       </c>
       <c r="C44">
-        <v>833.656501491331</v>
+        <v>776.7570751792528</v>
       </c>
       <c r="D44">
-        <v>2063.806501491331</v>
+        <v>2036.237075179253</v>
       </c>
       <c r="E44">
-        <v>710.1599999999999</v>
+        <v>739.49</v>
       </c>
       <c r="F44">
-        <v>1231.86</v>
+        <v>1261.19</v>
       </c>
       <c r="G44">
         <v>1.71</v>
@@ -4889,37 +4889,37 @@
         <v>157.65</v>
       </c>
       <c r="M44">
-        <v>180.837048</v>
+        <v>185.142692</v>
       </c>
       <c r="N44">
-        <v>-23.18704800000003</v>
+        <v>-27.49269200000006</v>
       </c>
       <c r="O44">
-        <v>-6.956114400000009</v>
+        <v>-8.247807600000018</v>
       </c>
       <c r="P44">
-        <v>-16.23093360000002</v>
+        <v>-19.24488440000005</v>
       </c>
       <c r="Q44">
-        <v>53.86906639999997</v>
+        <v>50.85511559999995</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1125948414412176</v>
+        <v>0.1137666807647477</v>
       </c>
       <c r="T44">
-        <v>0.9194561343495046</v>
+        <v>0.9355869437240573</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.261533798096505</v>
+        <v>0.2554516167454235</v>
       </c>
       <c r="W44">
-        <v>0.1084068384394331</v>
+        <v>0.1092997026617718</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8717793269883501</v>
+        <v>0.8515053891514116</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1118458801804681</v>
+        <v>0.1128558801804681</v>
       </c>
       <c r="C45">
-        <v>776.7570751792528</v>
+        <v>720.5845131836984</v>
       </c>
       <c r="D45">
-        <v>2036.237075179253</v>
+        <v>2009.394513183698</v>
       </c>
       <c r="E45">
-        <v>739.49</v>
+        <v>768.8199999999999</v>
       </c>
       <c r="F45">
-        <v>1261.19</v>
+        <v>1290.52</v>
       </c>
       <c r="G45">
         <v>1.71</v>
@@ -4971,37 +4971,37 @@
         <v>157.65</v>
       </c>
       <c r="M45">
-        <v>185.142692</v>
+        <v>189.448336</v>
       </c>
       <c r="N45">
-        <v>-27.49269200000006</v>
+        <v>-31.79833600000003</v>
       </c>
       <c r="O45">
-        <v>-8.247807600000018</v>
+        <v>-9.53950080000001</v>
       </c>
       <c r="P45">
-        <v>-19.24488440000005</v>
+        <v>-22.25883520000002</v>
       </c>
       <c r="Q45">
-        <v>50.85511559999995</v>
+        <v>47.84116479999997</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1137666807647477</v>
+        <v>0.1149803714926897</v>
       </c>
       <c r="T45">
-        <v>0.9355869437240573</v>
+        <v>0.9522938534334153</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2554516167454235</v>
+        <v>0.2496458981830275</v>
       </c>
       <c r="W45">
-        <v>0.1092997026617718</v>
+        <v>0.1101519821467316</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8515053891514116</v>
+        <v>0.8321529939434251</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1128558801804681</v>
+        <v>0.1138658801804681</v>
       </c>
       <c r="C46">
-        <v>720.5845131836984</v>
+        <v>665.1104439864839</v>
       </c>
       <c r="D46">
-        <v>2009.394513183698</v>
+        <v>1983.250443986484</v>
       </c>
       <c r="E46">
-        <v>768.8199999999999</v>
+        <v>798.1500000000001</v>
       </c>
       <c r="F46">
-        <v>1290.52</v>
+        <v>1319.85</v>
       </c>
       <c r="G46">
         <v>1.71</v>
@@ -5053,37 +5053,37 @@
         <v>157.65</v>
       </c>
       <c r="M46">
-        <v>189.448336</v>
+        <v>193.75398</v>
       </c>
       <c r="N46">
-        <v>-31.79833600000003</v>
+        <v>-36.10398000000006</v>
       </c>
       <c r="O46">
-        <v>-9.53950080000001</v>
+        <v>-10.83119400000002</v>
       </c>
       <c r="P46">
-        <v>-22.25883520000002</v>
+        <v>-25.27278600000005</v>
       </c>
       <c r="Q46">
-        <v>47.84116479999997</v>
+        <v>44.82721399999995</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1149803714926897</v>
+        <v>0.1162381964289204</v>
       </c>
       <c r="T46">
-        <v>0.9522938534334153</v>
+        <v>0.9696082871322047</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2496458981830275</v>
+        <v>0.244098211556738</v>
       </c>
       <c r="W46">
-        <v>0.1101519821467316</v>
+        <v>0.1109663825434709</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8321529939434251</v>
+        <v>0.8136607051891267</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1138658801804681</v>
+        <v>0.1410014984965226</v>
       </c>
       <c r="C47">
-        <v>665.1104439864839</v>
+        <v>122.0793457694238</v>
       </c>
       <c r="D47">
-        <v>1983.250443986484</v>
+        <v>1469.549345769424</v>
       </c>
       <c r="E47">
-        <v>798.1500000000001</v>
+        <v>827.48</v>
       </c>
       <c r="F47">
-        <v>1319.85</v>
+        <v>1349.18</v>
       </c>
       <c r="G47">
         <v>1.71</v>
@@ -5135,45 +5135,45 @@
         <v>157.65</v>
       </c>
       <c r="M47">
-        <v>193.75398</v>
+        <v>270.915344</v>
       </c>
       <c r="N47">
-        <v>-36.10398000000006</v>
+        <v>-113.265344</v>
       </c>
       <c r="O47">
-        <v>-10.83119400000002</v>
+        <v>-33.97960320000001</v>
       </c>
       <c r="P47">
-        <v>-25.27278600000005</v>
+        <v>-79.28574080000001</v>
       </c>
       <c r="Q47">
-        <v>44.82721399999995</v>
+        <v>-9.185740800000019</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1162381964289204</v>
+        <v>0.1199233821332606</v>
       </c>
       <c r="T47">
-        <v>0.9696082871322047</v>
+        <v>1.020336255474709</v>
       </c>
       <c r="U47">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.244098211556738</v>
+        <v>0.1745748295452766</v>
       </c>
       <c r="W47">
-        <v>0.1109663825434709</v>
+        <v>0.1657453742273085</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.8136607051891267</v>
+        <v>0.5819160984842555</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1410014984965226</v>
+        <v>0.1425514984965226</v>
       </c>
       <c r="C48">
-        <v>122.0793457694238</v>
+        <v>71.32386280788114</v>
       </c>
       <c r="D48">
-        <v>1469.549345769424</v>
+        <v>1448.123862807881</v>
       </c>
       <c r="E48">
-        <v>827.48</v>
+        <v>856.8099999999999</v>
       </c>
       <c r="F48">
-        <v>1349.18</v>
+        <v>1378.51</v>
       </c>
       <c r="G48">
         <v>1.71</v>
@@ -5217,37 +5217,37 @@
         <v>157.65</v>
       </c>
       <c r="M48">
-        <v>270.915344</v>
+        <v>276.804808</v>
       </c>
       <c r="N48">
-        <v>-113.265344</v>
+        <v>-119.154808</v>
       </c>
       <c r="O48">
-        <v>-33.97960320000001</v>
+        <v>-35.7464424</v>
       </c>
       <c r="P48">
-        <v>-79.28574080000001</v>
+        <v>-83.4083656</v>
       </c>
       <c r="Q48">
-        <v>-9.185740800000019</v>
+        <v>-13.3083656</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1199233821332606</v>
+        <v>0.1213219365131334</v>
       </c>
       <c r="T48">
-        <v>1.020336255474709</v>
+        <v>1.039587882936496</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1745748295452766</v>
+        <v>0.1708604714698453</v>
       </c>
       <c r="W48">
-        <v>0.1657453742273085</v>
+        <v>0.1664912173288551</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5819160984842555</v>
+        <v>0.5695349048994842</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1425514984965226</v>
+        <v>0.1441014984965226</v>
       </c>
       <c r="C49">
-        <v>71.32386280788114</v>
+        <v>21.18415324678699</v>
       </c>
       <c r="D49">
-        <v>1448.123862807881</v>
+        <v>1427.314153246787</v>
       </c>
       <c r="E49">
-        <v>856.8099999999999</v>
+        <v>886.1400000000001</v>
       </c>
       <c r="F49">
-        <v>1378.51</v>
+        <v>1407.84</v>
       </c>
       <c r="G49">
         <v>1.71</v>
@@ -5299,37 +5299,37 @@
         <v>157.65</v>
       </c>
       <c r="M49">
-        <v>276.804808</v>
+        <v>282.694272</v>
       </c>
       <c r="N49">
-        <v>-119.154808</v>
+        <v>-125.044272</v>
       </c>
       <c r="O49">
-        <v>-35.7464424</v>
+        <v>-37.51328160000001</v>
       </c>
       <c r="P49">
-        <v>-83.4083656</v>
+        <v>-87.53099040000004</v>
       </c>
       <c r="Q49">
-        <v>-13.3083656</v>
+        <v>-17.43099040000004</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1213219365131334</v>
+        <v>0.1227742814460783</v>
       </c>
       <c r="T49">
-        <v>1.039587882936496</v>
+        <v>1.059579957608352</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1708604714698453</v>
+        <v>0.1673008783142235</v>
       </c>
       <c r="W49">
-        <v>0.1664912173288551</v>
+        <v>0.1672059836345039</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5695349048994842</v>
+        <v>0.5576695943807449</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1441014984965226</v>
+        <v>0.1456514984965226</v>
       </c>
       <c r="C50">
-        <v>21.18415324678722</v>
+        <v>-28.36595305359788</v>
       </c>
       <c r="D50">
-        <v>1427.314153246787</v>
+        <v>1407.094046946402</v>
       </c>
       <c r="E50">
-        <v>886.1399999999999</v>
+        <v>915.47</v>
       </c>
       <c r="F50">
-        <v>1407.84</v>
+        <v>1437.17</v>
       </c>
       <c r="G50">
         <v>1.71</v>
@@ -5381,37 +5381,37 @@
         <v>157.65</v>
       </c>
       <c r="M50">
-        <v>282.694272</v>
+        <v>288.583736</v>
       </c>
       <c r="N50">
-        <v>-125.044272</v>
+        <v>-130.9337360000001</v>
       </c>
       <c r="O50">
-        <v>-37.51328160000001</v>
+        <v>-39.28012080000002</v>
       </c>
       <c r="P50">
-        <v>-87.53099040000004</v>
+        <v>-91.65361520000005</v>
       </c>
       <c r="Q50">
-        <v>-17.43099040000004</v>
+        <v>-21.55361520000005</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1227742814460783</v>
+        <v>0.1242835810822759</v>
       </c>
       <c r="T50">
-        <v>1.059579957608352</v>
+        <v>1.080356035208516</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1673008783142235</v>
+        <v>0.1638865746751577</v>
       </c>
       <c r="W50">
-        <v>0.1672059836345039</v>
+        <v>0.1678915758052283</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5576695943807449</v>
+        <v>0.5462885822505256</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1456514984965226</v>
+        <v>0.1472014984965226</v>
       </c>
       <c r="C51">
-        <v>-28.36595305359788</v>
+        <v>-77.35116398642595</v>
       </c>
       <c r="D51">
-        <v>1407.094046946402</v>
+        <v>1387.438836013574</v>
       </c>
       <c r="E51">
-        <v>915.47</v>
+        <v>944.8</v>
       </c>
       <c r="F51">
-        <v>1437.17</v>
+        <v>1466.5</v>
       </c>
       <c r="G51">
         <v>1.71</v>
@@ -5463,37 +5463,37 @@
         <v>157.65</v>
       </c>
       <c r="M51">
-        <v>288.583736</v>
+        <v>294.4732</v>
       </c>
       <c r="N51">
-        <v>-130.9337360000001</v>
+        <v>-136.8232</v>
       </c>
       <c r="O51">
-        <v>-39.28012080000002</v>
+        <v>-41.04696000000001</v>
       </c>
       <c r="P51">
-        <v>-91.65361520000005</v>
+        <v>-95.77624000000003</v>
       </c>
       <c r="Q51">
-        <v>-21.55361520000005</v>
+        <v>-25.67624000000004</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1242835810822759</v>
+        <v>0.1258532527039214</v>
       </c>
       <c r="T51">
-        <v>1.080356035208516</v>
+        <v>1.101963155912686</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1638865746751577</v>
+        <v>0.1606088431816545</v>
       </c>
       <c r="W51">
-        <v>0.1678915758052283</v>
+        <v>0.1685497442891238</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5462885822505256</v>
+        <v>0.535362810605515</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1472014984965226</v>
+        <v>0.1487514984965226</v>
       </c>
       <c r="C52">
-        <v>-77.35116398642595</v>
+        <v>-125.7948259194136</v>
       </c>
       <c r="D52">
-        <v>1387.438836013574</v>
+        <v>1368.325174080586</v>
       </c>
       <c r="E52">
-        <v>944.8</v>
+        <v>974.1299999999999</v>
       </c>
       <c r="F52">
-        <v>1466.5</v>
+        <v>1495.83</v>
       </c>
       <c r="G52">
         <v>1.71</v>
@@ -5545,37 +5545,37 @@
         <v>157.65</v>
       </c>
       <c r="M52">
-        <v>294.4732</v>
+        <v>300.362664</v>
       </c>
       <c r="N52">
-        <v>-136.8232</v>
+        <v>-142.712664</v>
       </c>
       <c r="O52">
-        <v>-41.04696000000001</v>
+        <v>-42.81379920000001</v>
       </c>
       <c r="P52">
-        <v>-95.77624000000003</v>
+        <v>-99.89886480000001</v>
       </c>
       <c r="Q52">
-        <v>-25.67624000000004</v>
+        <v>-29.79886480000002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1258532527039214</v>
+        <v>0.1274869925550219</v>
       </c>
       <c r="T52">
-        <v>1.101963155912686</v>
+        <v>1.124452199910904</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1606088431816545</v>
+        <v>0.1574596501780927</v>
       </c>
       <c r="W52">
-        <v>0.1685497442891238</v>
+        <v>0.169182102244239</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.535362810605515</v>
+        <v>0.5248655005936422</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1487514984965226</v>
+        <v>0.1503014984965226</v>
       </c>
       <c r="C53">
-        <v>-125.7948259194136</v>
+        <v>-173.719016203783</v>
       </c>
       <c r="D53">
-        <v>1368.325174080586</v>
+        <v>1349.730983796217</v>
       </c>
       <c r="E53">
-        <v>974.1299999999999</v>
+        <v>1003.46</v>
       </c>
       <c r="F53">
-        <v>1495.83</v>
+        <v>1525.16</v>
       </c>
       <c r="G53">
         <v>1.71</v>
@@ -5627,37 +5627,37 @@
         <v>157.65</v>
       </c>
       <c r="M53">
-        <v>300.362664</v>
+        <v>306.252128</v>
       </c>
       <c r="N53">
-        <v>-142.712664</v>
+        <v>-148.6021280000001</v>
       </c>
       <c r="O53">
-        <v>-42.81379920000001</v>
+        <v>-44.58063840000001</v>
       </c>
       <c r="P53">
-        <v>-99.89886480000001</v>
+        <v>-104.0214896</v>
       </c>
       <c r="Q53">
-        <v>-29.79886480000002</v>
+        <v>-33.92148960000004</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1274869925550219</v>
+        <v>0.1291888048999182</v>
       </c>
       <c r="T53">
-        <v>1.124452199910904</v>
+        <v>1.147878287409048</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1574596501780927</v>
+        <v>0.1544315799823601</v>
       </c>
       <c r="W53">
-        <v>0.169182102244239</v>
+        <v>0.1697901387395421</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5248655005936422</v>
+        <v>0.5147719332745337</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1503014984965226</v>
+        <v>0.1518514984965226</v>
       </c>
       <c r="C54">
-        <v>-173.719016203783</v>
+        <v>-221.1446282416946</v>
       </c>
       <c r="D54">
-        <v>1349.730983796217</v>
+        <v>1331.635371758305</v>
       </c>
       <c r="E54">
-        <v>1003.46</v>
+        <v>1032.79</v>
       </c>
       <c r="F54">
-        <v>1525.16</v>
+        <v>1554.49</v>
       </c>
       <c r="G54">
         <v>1.71</v>
@@ -5709,37 +5709,37 @@
         <v>157.65</v>
       </c>
       <c r="M54">
-        <v>306.252128</v>
+        <v>312.141592</v>
       </c>
       <c r="N54">
-        <v>-148.6021280000001</v>
+        <v>-154.491592</v>
       </c>
       <c r="O54">
-        <v>-44.58063840000001</v>
+        <v>-46.3474776</v>
       </c>
       <c r="P54">
-        <v>-104.0214896</v>
+        <v>-108.1441144</v>
       </c>
       <c r="Q54">
-        <v>-33.92148960000004</v>
+        <v>-38.04411440000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1291888048999182</v>
+        <v>0.1309630347914058</v>
       </c>
       <c r="T54">
-        <v>1.147878287409048</v>
+        <v>1.172301229694347</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1544315799823601</v>
+        <v>0.1515177765864665</v>
       </c>
       <c r="W54">
-        <v>0.1697901387395421</v>
+        <v>0.1703752304614375</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5147719332745337</v>
+        <v>0.5050592552882218</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1518514984965226</v>
+        <v>0.1728202610155978</v>
       </c>
       <c r="C55">
-        <v>-221.1446282416946</v>
+        <v>-454.914822184536</v>
       </c>
       <c r="D55">
-        <v>1331.635371758305</v>
+        <v>1127.195177815464</v>
       </c>
       <c r="E55">
-        <v>1032.79</v>
+        <v>1062.12</v>
       </c>
       <c r="F55">
-        <v>1554.49</v>
+        <v>1583.82</v>
       </c>
       <c r="G55">
         <v>1.71</v>
@@ -5791,45 +5791,45 @@
         <v>157.65</v>
       </c>
       <c r="M55">
-        <v>312.141592</v>
+        <v>373.4647560000001</v>
       </c>
       <c r="N55">
-        <v>-154.491592</v>
+        <v>-215.8147560000001</v>
       </c>
       <c r="O55">
-        <v>-46.3474776</v>
+        <v>-64.74442680000003</v>
       </c>
       <c r="P55">
-        <v>-108.1441144</v>
+        <v>-151.0703292000001</v>
       </c>
       <c r="Q55">
-        <v>-38.04411440000003</v>
+        <v>-80.97032920000007</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1309630347914058</v>
+        <v>0.1339421497196432</v>
       </c>
       <c r="T55">
-        <v>1.172301229694347</v>
+        <v>1.213309868035239</v>
       </c>
       <c r="U55">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1515177765864665</v>
+        <v>0.1266384558118785</v>
       </c>
       <c r="W55">
-        <v>0.1703752304614375</v>
+        <v>0.2059386521195591</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.5050592552882218</v>
+        <v>0.422128186039595</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1728202610155978</v>
+        <v>0.1747202610155978</v>
       </c>
       <c r="C56">
-        <v>-454.914822184536</v>
+        <v>-499.7102166610428</v>
       </c>
       <c r="D56">
-        <v>1127.195177815464</v>
+        <v>1111.729783338957</v>
       </c>
       <c r="E56">
-        <v>1062.12</v>
+        <v>1091.45</v>
       </c>
       <c r="F56">
-        <v>1583.82</v>
+        <v>1613.15</v>
       </c>
       <c r="G56">
         <v>1.71</v>
@@ -5873,37 +5873,37 @@
         <v>157.65</v>
       </c>
       <c r="M56">
-        <v>373.4647560000001</v>
+        <v>380.38077</v>
       </c>
       <c r="N56">
-        <v>-215.8147560000001</v>
+        <v>-222.7307700000001</v>
       </c>
       <c r="O56">
-        <v>-64.74442680000003</v>
+        <v>-66.81923100000002</v>
       </c>
       <c r="P56">
-        <v>-151.0703292000001</v>
+        <v>-155.9115390000001</v>
       </c>
       <c r="Q56">
-        <v>-80.97032920000007</v>
+        <v>-85.81153900000007</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1339421497196432</v>
+        <v>0.1359008641578575</v>
       </c>
       <c r="T56">
-        <v>1.213309868035239</v>
+        <v>1.240272309547133</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1266384558118785</v>
+        <v>0.1243359384334807</v>
       </c>
       <c r="W56">
-        <v>0.2059386521195591</v>
+        <v>0.2064815857173853</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.422128186039595</v>
+        <v>0.4144531281116024</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1747202610155978</v>
+        <v>0.1766202610155978</v>
       </c>
       <c r="C57">
-        <v>-499.7102166610428</v>
+        <v>-544.0869768867251</v>
       </c>
       <c r="D57">
-        <v>1111.729783338957</v>
+        <v>1096.683023113275</v>
       </c>
       <c r="E57">
-        <v>1091.45</v>
+        <v>1120.78</v>
       </c>
       <c r="F57">
-        <v>1613.15</v>
+        <v>1642.48</v>
       </c>
       <c r="G57">
         <v>1.71</v>
@@ -5955,37 +5955,37 @@
         <v>157.65</v>
       </c>
       <c r="M57">
-        <v>380.38077</v>
+        <v>387.2967840000001</v>
       </c>
       <c r="N57">
-        <v>-222.7307700000001</v>
+        <v>-229.6467840000001</v>
       </c>
       <c r="O57">
-        <v>-66.81923100000002</v>
+        <v>-68.89403520000002</v>
       </c>
       <c r="P57">
-        <v>-155.9115390000001</v>
+        <v>-160.7527488000001</v>
       </c>
       <c r="Q57">
-        <v>-85.81153900000007</v>
+        <v>-90.65274880000007</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1359008641578575</v>
+        <v>0.1379486110705361</v>
       </c>
       <c r="T57">
-        <v>1.240272309547133</v>
+        <v>1.268460316582295</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1243359384334807</v>
+        <v>0.1221156538185971</v>
       </c>
       <c r="W57">
-        <v>0.2064815857173853</v>
+        <v>0.2070051288295748</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4144531281116024</v>
+        <v>0.4070521793953238</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1766202610155978</v>
+        <v>0.1785202610155978</v>
       </c>
       <c r="C58">
-        <v>-544.0869768867251</v>
+        <v>-588.0618739487088</v>
       </c>
       <c r="D58">
-        <v>1096.683023113275</v>
+        <v>1082.038126051291</v>
       </c>
       <c r="E58">
-        <v>1120.78</v>
+        <v>1150.11</v>
       </c>
       <c r="F58">
-        <v>1642.48</v>
+        <v>1671.81</v>
       </c>
       <c r="G58">
         <v>1.71</v>
@@ -6037,37 +6037,37 @@
         <v>157.65</v>
       </c>
       <c r="M58">
-        <v>387.2967840000001</v>
+        <v>394.2127980000001</v>
       </c>
       <c r="N58">
-        <v>-229.6467840000001</v>
+        <v>-236.5627980000001</v>
       </c>
       <c r="O58">
-        <v>-68.89403520000002</v>
+        <v>-70.96883940000002</v>
       </c>
       <c r="P58">
-        <v>-160.7527488000001</v>
+        <v>-165.5939586000001</v>
       </c>
       <c r="Q58">
-        <v>-90.65274880000007</v>
+        <v>-95.49395860000007</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1379486110705361</v>
+        <v>0.1400916020256649</v>
       </c>
       <c r="T58">
-        <v>1.268460316582295</v>
+        <v>1.297959393712116</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1221156538185971</v>
+        <v>0.1199732739270428</v>
       </c>
       <c r="W58">
-        <v>0.2070051288295748</v>
+        <v>0.2075103020080033</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4070521793953238</v>
+        <v>0.3999109130901426</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1785202610155978</v>
+        <v>0.1804202610155978</v>
       </c>
       <c r="C59">
-        <v>-588.0618739487088</v>
+        <v>-631.6507949075769</v>
       </c>
       <c r="D59">
-        <v>1082.038126051291</v>
+        <v>1067.779205092423</v>
       </c>
       <c r="E59">
-        <v>1150.11</v>
+        <v>1179.44</v>
       </c>
       <c r="F59">
-        <v>1671.81</v>
+        <v>1701.14</v>
       </c>
       <c r="G59">
         <v>1.71</v>
@@ -6119,37 +6119,37 @@
         <v>157.65</v>
       </c>
       <c r="M59">
-        <v>394.2127980000001</v>
+        <v>401.128812</v>
       </c>
       <c r="N59">
-        <v>-236.5627980000001</v>
+        <v>-243.4788120000001</v>
       </c>
       <c r="O59">
-        <v>-70.96883940000002</v>
+        <v>-73.04364360000001</v>
       </c>
       <c r="P59">
-        <v>-165.5939586000001</v>
+        <v>-170.4351684000001</v>
       </c>
       <c r="Q59">
-        <v>-95.49395860000007</v>
+        <v>-100.3351684000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1400916020256649</v>
+        <v>0.1423366401691331</v>
       </c>
       <c r="T59">
-        <v>1.297959393712116</v>
+        <v>1.3288631888005</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1199732739270428</v>
+        <v>0.1179047692041627</v>
       </c>
       <c r="W59">
-        <v>0.2075103020080033</v>
+        <v>0.2079980554216584</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3999109130901426</v>
+        <v>0.3930158973472092</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1804202610155978</v>
+        <v>0.1823202610155978</v>
       </c>
       <c r="C60">
-        <v>-631.6507949075765</v>
+        <v>-674.868800287559</v>
       </c>
       <c r="D60">
-        <v>1067.779205092423</v>
+        <v>1053.891199712441</v>
       </c>
       <c r="E60">
-        <v>1179.44</v>
+        <v>1208.77</v>
       </c>
       <c r="F60">
-        <v>1701.14</v>
+        <v>1730.47</v>
       </c>
       <c r="G60">
         <v>1.71</v>
@@ -6201,37 +6201,37 @@
         <v>157.65</v>
       </c>
       <c r="M60">
-        <v>401.128812</v>
+        <v>408.0448259999999</v>
       </c>
       <c r="N60">
-        <v>-243.478812</v>
+        <v>-250.394826</v>
       </c>
       <c r="O60">
-        <v>-73.0436436</v>
+        <v>-75.11844779999998</v>
       </c>
       <c r="P60">
-        <v>-170.4351684</v>
+        <v>-175.2763782</v>
       </c>
       <c r="Q60">
-        <v>-100.3351684</v>
+        <v>-105.1763782</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1423366401691331</v>
+        <v>0.1446911923683802</v>
       </c>
       <c r="T60">
-        <v>1.328863188800499</v>
+        <v>1.361274486088316</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1179047692041628</v>
+        <v>0.1159063832854481</v>
       </c>
       <c r="W60">
-        <v>0.2079980554216584</v>
+        <v>0.2084692748212914</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3930158973472092</v>
+        <v>0.3863546109514938</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1823202610155978</v>
+        <v>0.1842202610155978</v>
       </c>
       <c r="C61">
-        <v>-674.868800287559</v>
+        <v>-717.7301771378668</v>
       </c>
       <c r="D61">
-        <v>1053.891199712441</v>
+        <v>1040.359822862133</v>
       </c>
       <c r="E61">
-        <v>1208.77</v>
+        <v>1238.1</v>
       </c>
       <c r="F61">
-        <v>1730.47</v>
+        <v>1759.8</v>
       </c>
       <c r="G61">
         <v>1.71</v>
@@ -6283,37 +6283,37 @@
         <v>157.65</v>
       </c>
       <c r="M61">
-        <v>408.0448259999999</v>
+        <v>414.96084</v>
       </c>
       <c r="N61">
-        <v>-250.394826</v>
+        <v>-257.31084</v>
       </c>
       <c r="O61">
-        <v>-75.11844779999998</v>
+        <v>-77.19325200000002</v>
       </c>
       <c r="P61">
-        <v>-175.2763782</v>
+        <v>-180.117588</v>
       </c>
       <c r="Q61">
-        <v>-105.1763782</v>
+        <v>-110.017588</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1446911923683802</v>
+        <v>0.1471634721775897</v>
       </c>
       <c r="T61">
-        <v>1.361274486088316</v>
+        <v>1.395306348240524</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1159063832854481</v>
+        <v>0.1139746102306907</v>
       </c>
       <c r="W61">
-        <v>0.2084692748212914</v>
+        <v>0.2089247869076032</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3863546109514938</v>
+        <v>0.3799153674356356</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1842202610155978</v>
+        <v>0.1861202610155978</v>
       </c>
       <c r="C62">
-        <v>-717.7301771378668</v>
+        <v>-760.2484880581751</v>
       </c>
       <c r="D62">
-        <v>1040.359822862133</v>
+        <v>1027.171511941825</v>
       </c>
       <c r="E62">
-        <v>1238.1</v>
+        <v>1267.43</v>
       </c>
       <c r="F62">
-        <v>1759.8</v>
+        <v>1789.13</v>
       </c>
       <c r="G62">
         <v>1.71</v>
@@ -6365,37 +6365,37 @@
         <v>157.65</v>
       </c>
       <c r="M62">
-        <v>414.96084</v>
+        <v>421.876854</v>
       </c>
       <c r="N62">
-        <v>-257.31084</v>
+        <v>-264.226854</v>
       </c>
       <c r="O62">
-        <v>-77.19325200000002</v>
+        <v>-79.2680562</v>
       </c>
       <c r="P62">
-        <v>-180.117588</v>
+        <v>-184.9587978</v>
       </c>
       <c r="Q62">
-        <v>-110.017588</v>
+        <v>-114.8587978</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1471634721775897</v>
+        <v>0.1497625355667587</v>
       </c>
       <c r="T62">
-        <v>1.395306348240524</v>
+        <v>1.431083434092846</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1139746102306907</v>
+        <v>0.1121061739974007</v>
       </c>
       <c r="W62">
-        <v>0.2089247869076032</v>
+        <v>0.2093653641714129</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3799153674356356</v>
+        <v>0.3736872466580022</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1861202610155978</v>
+        <v>0.1880202610155978</v>
       </c>
       <c r="C63">
-        <v>-760.2484880581751</v>
+        <v>-802.4366165419091</v>
       </c>
       <c r="D63">
-        <v>1027.171511941825</v>
+        <v>1014.313383458091</v>
       </c>
       <c r="E63">
-        <v>1267.43</v>
+        <v>1296.76</v>
       </c>
       <c r="F63">
-        <v>1789.13</v>
+        <v>1818.46</v>
       </c>
       <c r="G63">
         <v>1.71</v>
@@ -6447,37 +6447,37 @@
         <v>157.65</v>
       </c>
       <c r="M63">
-        <v>421.876854</v>
+        <v>428.792868</v>
       </c>
       <c r="N63">
-        <v>-264.226854</v>
+        <v>-271.142868</v>
       </c>
       <c r="O63">
-        <v>-79.2680562</v>
+        <v>-81.34286040000001</v>
       </c>
       <c r="P63">
-        <v>-184.9587978</v>
+        <v>-189.8000076</v>
       </c>
       <c r="Q63">
-        <v>-114.8587978</v>
+        <v>-119.7000076</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1497625355667587</v>
+        <v>0.1524983917658839</v>
       </c>
       <c r="T63">
-        <v>1.431083434092846</v>
+        <v>1.46874352446371</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1121061739974007</v>
+        <v>0.1102980099006684</v>
       </c>
       <c r="W63">
-        <v>0.2093653641714129</v>
+        <v>0.2097917292654224</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3736872466580022</v>
+        <v>0.3676600330022279</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1880202610155978</v>
+        <v>0.1899202610155978</v>
       </c>
       <c r="C64">
-        <v>-802.4366165419091</v>
+        <v>-844.3068089559811</v>
       </c>
       <c r="D64">
-        <v>1014.313383458091</v>
+        <v>1001.773191044019</v>
       </c>
       <c r="E64">
-        <v>1296.76</v>
+        <v>1326.09</v>
       </c>
       <c r="F64">
-        <v>1818.46</v>
+        <v>1847.79</v>
       </c>
       <c r="G64">
         <v>1.71</v>
@@ -6529,37 +6529,37 @@
         <v>157.65</v>
       </c>
       <c r="M64">
-        <v>428.792868</v>
+        <v>435.708882</v>
       </c>
       <c r="N64">
-        <v>-271.142868</v>
+        <v>-278.058882</v>
       </c>
       <c r="O64">
-        <v>-81.34286040000001</v>
+        <v>-83.41766460000001</v>
       </c>
       <c r="P64">
-        <v>-189.8000076</v>
+        <v>-194.6412174</v>
       </c>
       <c r="Q64">
-        <v>-119.7000076</v>
+        <v>-124.5412174</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1524983917658839</v>
+        <v>0.1553821320838808</v>
       </c>
       <c r="T64">
-        <v>1.46874352446371</v>
+        <v>1.508439295395162</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1102980099006684</v>
+        <v>0.108547247838753</v>
       </c>
       <c r="W64">
-        <v>0.2097917292654224</v>
+        <v>0.210204558959622</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3676600330022279</v>
+        <v>0.36182415946251</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1899202610155978</v>
+        <v>0.1918202610155978</v>
       </c>
       <c r="C65">
-        <v>-844.3068089559811</v>
+        <v>-885.8707134445359</v>
       </c>
       <c r="D65">
-        <v>1001.773191044019</v>
+        <v>989.5392865554642</v>
       </c>
       <c r="E65">
-        <v>1326.09</v>
+        <v>1355.42</v>
       </c>
       <c r="F65">
-        <v>1847.79</v>
+        <v>1877.12</v>
       </c>
       <c r="G65">
         <v>1.71</v>
@@ -6611,37 +6611,37 @@
         <v>157.65</v>
       </c>
       <c r="M65">
-        <v>435.708882</v>
+        <v>442.624896</v>
       </c>
       <c r="N65">
-        <v>-278.058882</v>
+        <v>-284.9748960000001</v>
       </c>
       <c r="O65">
-        <v>-83.41766460000001</v>
+        <v>-85.49246880000001</v>
       </c>
       <c r="P65">
-        <v>-194.6412174</v>
+        <v>-199.4824272</v>
       </c>
       <c r="Q65">
-        <v>-124.5412174</v>
+        <v>-129.3824272000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1553821320838808</v>
+        <v>0.1584260801973219</v>
       </c>
       <c r="T65">
-        <v>1.508439295395162</v>
+        <v>1.550340386933916</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.108547247838753</v>
+        <v>0.1068511970912725</v>
       </c>
       <c r="W65">
-        <v>0.210204558959622</v>
+        <v>0.210604487725878</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.36182415946251</v>
+        <v>0.3561706569709083</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1918202610155978</v>
+        <v>0.1937202610155978</v>
       </c>
       <c r="C66">
-        <v>-885.8707134445359</v>
+        <v>-927.1394160164679</v>
       </c>
       <c r="D66">
-        <v>989.5392865554642</v>
+        <v>977.6005839835321</v>
       </c>
       <c r="E66">
-        <v>1355.42</v>
+        <v>1384.75</v>
       </c>
       <c r="F66">
-        <v>1877.12</v>
+        <v>1906.45</v>
       </c>
       <c r="G66">
         <v>1.71</v>
@@ -6693,37 +6693,37 @@
         <v>157.65</v>
       </c>
       <c r="M66">
-        <v>442.624896</v>
+        <v>449.5409100000001</v>
       </c>
       <c r="N66">
-        <v>-284.9748960000001</v>
+        <v>-291.8909100000001</v>
       </c>
       <c r="O66">
-        <v>-85.49246880000001</v>
+        <v>-87.56727300000001</v>
       </c>
       <c r="P66">
-        <v>-199.4824272</v>
+        <v>-204.3236370000001</v>
       </c>
       <c r="Q66">
-        <v>-129.3824272000001</v>
+        <v>-134.2236370000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1584260801973219</v>
+        <v>0.1616439682029597</v>
       </c>
       <c r="T66">
-        <v>1.550340386933916</v>
+        <v>1.594635826560599</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1068511970912725</v>
+        <v>0.1052073325206375</v>
       </c>
       <c r="W66">
-        <v>0.210604487725878</v>
+        <v>0.2109921109916337</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3561706569709083</v>
+        <v>0.3506911084021251</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1937202610155978</v>
+        <v>0.1956202610155978</v>
       </c>
       <c r="C67">
-        <v>-927.1394160164679</v>
+        <v>-968.1234740517283</v>
       </c>
       <c r="D67">
-        <v>977.6005839835321</v>
+        <v>965.9465259482719</v>
       </c>
       <c r="E67">
-        <v>1384.75</v>
+        <v>1414.08</v>
       </c>
       <c r="F67">
-        <v>1906.45</v>
+        <v>1935.78</v>
       </c>
       <c r="G67">
         <v>1.71</v>
@@ -6775,37 +6775,37 @@
         <v>157.65</v>
       </c>
       <c r="M67">
-        <v>449.5409100000001</v>
+        <v>456.4569240000001</v>
       </c>
       <c r="N67">
-        <v>-291.8909100000001</v>
+        <v>-298.8069240000001</v>
       </c>
       <c r="O67">
-        <v>-87.56727300000001</v>
+        <v>-89.64207720000003</v>
       </c>
       <c r="P67">
-        <v>-204.3236370000001</v>
+        <v>-209.1648468000001</v>
       </c>
       <c r="Q67">
-        <v>-134.2236370000001</v>
+        <v>-139.0648468000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1616439682029597</v>
+        <v>0.1650511437383408</v>
       </c>
       <c r="T67">
-        <v>1.594635826560599</v>
+        <v>1.64153688028297</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1052073325206375</v>
+        <v>0.1036132820279006</v>
       </c>
       <c r="W67">
-        <v>0.2109921109916337</v>
+        <v>0.2113679880978211</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3506911084021251</v>
+        <v>0.3453776067596687</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1956202610155978</v>
+        <v>0.1975202610155978</v>
       </c>
       <c r="C68">
-        <v>-968.1234740517283</v>
+        <v>-1008.832947439274</v>
       </c>
       <c r="D68">
-        <v>965.9465259482719</v>
+        <v>954.567052560726</v>
       </c>
       <c r="E68">
-        <v>1414.08</v>
+        <v>1443.41</v>
       </c>
       <c r="F68">
-        <v>1935.78</v>
+        <v>1965.11</v>
       </c>
       <c r="G68">
         <v>1.71</v>
@@ -6857,37 +6857,37 @@
         <v>157.65</v>
       </c>
       <c r="M68">
-        <v>456.4569240000001</v>
+        <v>463.372938</v>
       </c>
       <c r="N68">
-        <v>-298.8069240000001</v>
+        <v>-305.7229380000001</v>
       </c>
       <c r="O68">
-        <v>-89.64207720000003</v>
+        <v>-91.71688140000002</v>
       </c>
       <c r="P68">
-        <v>-209.1648468000001</v>
+        <v>-214.0060566</v>
       </c>
       <c r="Q68">
-        <v>-139.0648468000001</v>
+        <v>-143.9060566</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1650511437383408</v>
+        <v>0.1686648147607148</v>
       </c>
       <c r="T68">
-        <v>1.64153688028297</v>
+        <v>1.691280422109727</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1036132820279006</v>
+        <v>0.1020668151319618</v>
       </c>
       <c r="W68">
-        <v>0.2113679880978211</v>
+        <v>0.2117326449918834</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3453776067596687</v>
+        <v>0.3402227171065393</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1975202610155978</v>
+        <v>0.1994202610155978</v>
       </c>
       <c r="C69">
-        <v>-1008.832947439274</v>
+        <v>-1049.277427539696</v>
       </c>
       <c r="D69">
-        <v>954.567052560726</v>
+        <v>943.4525724603036</v>
       </c>
       <c r="E69">
-        <v>1443.41</v>
+        <v>1472.74</v>
       </c>
       <c r="F69">
-        <v>1965.11</v>
+        <v>1994.44</v>
       </c>
       <c r="G69">
         <v>1.71</v>
@@ -6939,37 +6939,37 @@
         <v>157.65</v>
       </c>
       <c r="M69">
-        <v>463.372938</v>
+        <v>470.2889520000001</v>
       </c>
       <c r="N69">
-        <v>-305.7229380000001</v>
+        <v>-312.6389520000001</v>
       </c>
       <c r="O69">
-        <v>-91.71688140000002</v>
+        <v>-93.79168560000002</v>
       </c>
       <c r="P69">
-        <v>-214.0060566</v>
+        <v>-218.8472664000001</v>
       </c>
       <c r="Q69">
-        <v>-143.9060566</v>
+        <v>-148.7472664000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1686648147607148</v>
+        <v>0.1725043402219872</v>
       </c>
       <c r="T69">
-        <v>1.691280422109727</v>
+        <v>1.744132935300656</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1020668151319618</v>
+        <v>0.1005658325564917</v>
       </c>
       <c r="W69">
-        <v>0.2117326449918834</v>
+        <v>0.2120865766831793</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3402227171065393</v>
+        <v>0.3352194418549725</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1994202610155978</v>
+        <v>0.2013202610155978</v>
       </c>
       <c r="C70">
-        <v>-1049.277427539696</v>
+        <v>-1089.466064147778</v>
       </c>
       <c r="D70">
-        <v>943.4525724603036</v>
+        <v>932.5939358522227</v>
       </c>
       <c r="E70">
-        <v>1472.74</v>
+        <v>1502.07</v>
       </c>
       <c r="F70">
-        <v>1994.44</v>
+        <v>2023.77</v>
       </c>
       <c r="G70">
         <v>1.71</v>
@@ -7021,37 +7021,37 @@
         <v>157.65</v>
       </c>
       <c r="M70">
-        <v>470.2889520000001</v>
+        <v>477.2049660000001</v>
       </c>
       <c r="N70">
-        <v>-312.6389520000001</v>
+        <v>-319.5549660000001</v>
       </c>
       <c r="O70">
-        <v>-93.79168560000002</v>
+        <v>-95.86648980000002</v>
       </c>
       <c r="P70">
-        <v>-218.8472664000001</v>
+        <v>-223.6884762000001</v>
       </c>
       <c r="Q70">
-        <v>-148.7472664000001</v>
+        <v>-153.5884762000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1725043402219872</v>
+        <v>0.1765915770033416</v>
       </c>
       <c r="T70">
-        <v>1.744132935300656</v>
+        <v>1.80039528805229</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1005658325564917</v>
+        <v>0.0991083567223397</v>
       </c>
       <c r="W70">
-        <v>0.2120865766831793</v>
+        <v>0.2124302494848723</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3352194418549725</v>
+        <v>0.3303611890744657</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2013202610155978</v>
+        <v>0.2032202610155978</v>
       </c>
       <c r="C71">
-        <v>-1089.466064147778</v>
+        <v>-1129.407590614291</v>
       </c>
       <c r="D71">
-        <v>932.5939358522227</v>
+        <v>921.9824093857096</v>
       </c>
       <c r="E71">
-        <v>1502.07</v>
+        <v>1531.4</v>
       </c>
       <c r="F71">
-        <v>2023.77</v>
+        <v>2053.1</v>
       </c>
       <c r="G71">
         <v>1.71</v>
@@ -7103,37 +7103,37 @@
         <v>157.65</v>
       </c>
       <c r="M71">
-        <v>477.2049660000001</v>
+        <v>484.1209800000001</v>
       </c>
       <c r="N71">
-        <v>-319.5549660000001</v>
+        <v>-326.4709800000001</v>
       </c>
       <c r="O71">
-        <v>-95.86648980000002</v>
+        <v>-97.94129400000003</v>
       </c>
       <c r="P71">
-        <v>-223.6884762000001</v>
+        <v>-228.5296860000001</v>
       </c>
       <c r="Q71">
-        <v>-153.5884762000001</v>
+        <v>-158.4296860000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1765915770033416</v>
+        <v>0.1809512962367863</v>
       </c>
       <c r="T71">
-        <v>1.80039528805229</v>
+        <v>1.8604084643207</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0991083567223397</v>
+        <v>0.09769252305487769</v>
       </c>
       <c r="W71">
-        <v>0.2124302494848723</v>
+        <v>0.2127641030636598</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3303611890744657</v>
+        <v>0.325641743516259</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2032202610155978</v>
+        <v>0.2051202610155978</v>
       </c>
       <c r="C72">
-        <v>-1129.407590614291</v>
+        <v>-1169.110347272001</v>
       </c>
       <c r="D72">
-        <v>921.9824093857096</v>
+        <v>911.6096527279987</v>
       </c>
       <c r="E72">
-        <v>1531.4</v>
+        <v>1560.73</v>
       </c>
       <c r="F72">
-        <v>2053.1</v>
+        <v>2082.43</v>
       </c>
       <c r="G72">
         <v>1.71</v>
@@ -7185,37 +7185,37 @@
         <v>157.65</v>
       </c>
       <c r="M72">
-        <v>484.1209800000001</v>
+        <v>491.0369940000001</v>
       </c>
       <c r="N72">
-        <v>-326.4709800000001</v>
+        <v>-333.3869940000001</v>
       </c>
       <c r="O72">
-        <v>-97.94129400000003</v>
+        <v>-100.0160982</v>
       </c>
       <c r="P72">
-        <v>-228.5296860000001</v>
+        <v>-233.3708958000001</v>
       </c>
       <c r="Q72">
-        <v>-158.4296860000001</v>
+        <v>-163.2708958000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1809512962367863</v>
+        <v>0.1856116857621928</v>
       </c>
       <c r="T72">
-        <v>1.8604084643207</v>
+        <v>1.924560480331758</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09769252305487769</v>
+        <v>0.09631657202593576</v>
       </c>
       <c r="W72">
-        <v>0.2127641030636598</v>
+        <v>0.2130885523162843</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.325641743516259</v>
+        <v>0.3210552400864525</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2051202610155978</v>
+        <v>0.2070202610155978</v>
       </c>
       <c r="C73">
-        <v>-1169.110347272001</v>
+        <v>-1208.582303297938</v>
       </c>
       <c r="D73">
-        <v>911.6096527279987</v>
+        <v>901.4676967020614</v>
       </c>
       <c r="E73">
-        <v>1560.73</v>
+        <v>1590.06</v>
       </c>
       <c r="F73">
-        <v>2082.43</v>
+        <v>2111.76</v>
       </c>
       <c r="G73">
         <v>1.71</v>
@@ -7267,37 +7267,37 @@
         <v>157.65</v>
       </c>
       <c r="M73">
-        <v>491.036994</v>
+        <v>497.953008</v>
       </c>
       <c r="N73">
-        <v>-333.386994</v>
+        <v>-340.303008</v>
       </c>
       <c r="O73">
-        <v>-100.0160982</v>
+        <v>-102.0909024</v>
       </c>
       <c r="P73">
-        <v>-233.3708958</v>
+        <v>-238.2121056</v>
       </c>
       <c r="Q73">
-        <v>-163.2708958</v>
+        <v>-168.1121056</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1856116857621927</v>
+        <v>0.1906049602536996</v>
       </c>
       <c r="T73">
-        <v>1.924560480331758</v>
+        <v>1.993294783200749</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09631657202593577</v>
+        <v>0.0949788418589089</v>
       </c>
       <c r="W73">
-        <v>0.2130885523162843</v>
+        <v>0.2134039890896693</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3210552400864526</v>
+        <v>0.3165961395296963</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2070202610155978</v>
+        <v>0.2089202610155978</v>
       </c>
       <c r="C74">
-        <v>-1208.582303297938</v>
+        <v>-1247.831077132372</v>
       </c>
       <c r="D74">
-        <v>901.4676967020614</v>
+        <v>891.548922867628</v>
       </c>
       <c r="E74">
-        <v>1590.06</v>
+        <v>1619.39</v>
       </c>
       <c r="F74">
-        <v>2111.76</v>
+        <v>2141.09</v>
       </c>
       <c r="G74">
         <v>1.71</v>
@@ -7349,37 +7349,37 @@
         <v>157.65</v>
       </c>
       <c r="M74">
-        <v>497.953008</v>
+        <v>504.869022</v>
       </c>
       <c r="N74">
-        <v>-340.303008</v>
+        <v>-347.2190220000001</v>
       </c>
       <c r="O74">
-        <v>-102.0909024</v>
+        <v>-104.1657066</v>
       </c>
       <c r="P74">
-        <v>-238.2121056</v>
+        <v>-243.0533154</v>
       </c>
       <c r="Q74">
-        <v>-168.1121056</v>
+        <v>-172.9533154</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1906049602536996</v>
+        <v>0.1959681069297625</v>
       </c>
       <c r="T74">
-        <v>1.993294783200749</v>
+        <v>2.067120515911888</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0949788418589089</v>
+        <v>0.09367776183344438</v>
       </c>
       <c r="W74">
-        <v>0.2134039890896693</v>
+        <v>0.2137107837596738</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3165961395296963</v>
+        <v>0.3122592061114813</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2089202610155978</v>
+        <v>0.2108202610155978</v>
       </c>
       <c r="C75">
-        <v>-1247.831077132372</v>
+        <v>-1286.86395556445</v>
       </c>
       <c r="D75">
-        <v>891.548922867628</v>
+        <v>881.8460444355499</v>
       </c>
       <c r="E75">
-        <v>1619.39</v>
+        <v>1648.72</v>
       </c>
       <c r="F75">
-        <v>2141.09</v>
+        <v>2170.42</v>
       </c>
       <c r="G75">
         <v>1.71</v>
@@ -7431,37 +7431,37 @@
         <v>157.65</v>
       </c>
       <c r="M75">
-        <v>504.869022</v>
+        <v>511.785036</v>
       </c>
       <c r="N75">
-        <v>-347.2190220000001</v>
+        <v>-354.1350360000001</v>
       </c>
       <c r="O75">
-        <v>-104.1657066</v>
+        <v>-106.2405108</v>
       </c>
       <c r="P75">
-        <v>-243.0533154</v>
+        <v>-247.8945252</v>
       </c>
       <c r="Q75">
-        <v>-172.9533154</v>
+        <v>-177.7945252</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1959681069297625</v>
+        <v>0.201743803350138</v>
       </c>
       <c r="T75">
-        <v>2.067120515911888</v>
+        <v>2.146625151139268</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09367776183344438</v>
+        <v>0.09241184613299243</v>
       </c>
       <c r="W75">
-        <v>0.2137107837596738</v>
+        <v>0.2140092866818404</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3122592061114813</v>
+        <v>0.3080394871099748</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2108202610155978</v>
+        <v>0.2127202610155978</v>
       </c>
       <c r="C76">
-        <v>-1286.86395556445</v>
+        <v>-1325.687911584985</v>
       </c>
       <c r="D76">
-        <v>881.8460444355499</v>
+        <v>872.3520884150147</v>
       </c>
       <c r="E76">
-        <v>1648.72</v>
+        <v>1678.05</v>
       </c>
       <c r="F76">
-        <v>2170.42</v>
+        <v>2199.75</v>
       </c>
       <c r="G76">
         <v>1.71</v>
@@ -7513,37 +7513,37 @@
         <v>157.65</v>
       </c>
       <c r="M76">
-        <v>511.785036</v>
+        <v>518.70105</v>
       </c>
       <c r="N76">
-        <v>-354.1350360000001</v>
+        <v>-361.05105</v>
       </c>
       <c r="O76">
-        <v>-106.2405108</v>
+        <v>-108.315315</v>
       </c>
       <c r="P76">
-        <v>-247.8945252</v>
+        <v>-252.735735</v>
       </c>
       <c r="Q76">
-        <v>-177.7945252</v>
+        <v>-182.635735</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.201743803350138</v>
+        <v>0.2079815554841435</v>
       </c>
       <c r="T76">
-        <v>2.146625151139268</v>
+        <v>2.232490157184839</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09241184613299243</v>
+        <v>0.09117968818455253</v>
       </c>
       <c r="W76">
-        <v>0.2140092866818404</v>
+        <v>0.2142998295260825</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3080394871099748</v>
+        <v>0.3039322939485084</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2127202610155978</v>
+        <v>0.2146202610155978</v>
       </c>
       <c r="C77">
-        <v>-1325.687911584985</v>
+        <v>-1364.309621098298</v>
       </c>
       <c r="D77">
-        <v>872.3520884150147</v>
+        <v>863.0603789017019</v>
       </c>
       <c r="E77">
-        <v>1678.05</v>
+        <v>1707.38</v>
       </c>
       <c r="F77">
-        <v>2199.75</v>
+        <v>2229.08</v>
       </c>
       <c r="G77">
         <v>1.71</v>
@@ -7595,37 +7595,37 @@
         <v>157.65</v>
       </c>
       <c r="M77">
-        <v>518.70105</v>
+        <v>525.617064</v>
       </c>
       <c r="N77">
-        <v>-361.05105</v>
+        <v>-367.9670640000001</v>
       </c>
       <c r="O77">
-        <v>-108.315315</v>
+        <v>-110.3901192</v>
       </c>
       <c r="P77">
-        <v>-252.735735</v>
+        <v>-257.5769448</v>
       </c>
       <c r="Q77">
-        <v>-182.635735</v>
+        <v>-187.4769448</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2079815554841435</v>
+        <v>0.2147391202959829</v>
       </c>
       <c r="T77">
-        <v>2.232490157184839</v>
+        <v>2.325510580400874</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09117968818455253</v>
+        <v>0.0899799554452821</v>
       </c>
       <c r="W77">
-        <v>0.2142998295260825</v>
+        <v>0.2145827265060025</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3039322939485084</v>
+        <v>0.299933184817607</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2146202610155978</v>
+        <v>0.2165202610155978</v>
       </c>
       <c r="C78">
-        <v>-1364.309621098298</v>
+        <v>-1402.735478577302</v>
       </c>
       <c r="D78">
-        <v>863.0603789017019</v>
+        <v>853.9645214226974</v>
       </c>
       <c r="E78">
-        <v>1707.38</v>
+        <v>1736.71</v>
       </c>
       <c r="F78">
-        <v>2229.08</v>
+        <v>2258.41</v>
       </c>
       <c r="G78">
         <v>1.71</v>
@@ -7677,37 +7677,37 @@
         <v>157.65</v>
       </c>
       <c r="M78">
-        <v>525.617064</v>
+        <v>532.5330779999999</v>
       </c>
       <c r="N78">
-        <v>-367.9670640000001</v>
+        <v>-374.883078</v>
       </c>
       <c r="O78">
-        <v>-110.3901192</v>
+        <v>-112.4649234</v>
       </c>
       <c r="P78">
-        <v>-257.5769448</v>
+        <v>-262.4181546</v>
       </c>
       <c r="Q78">
-        <v>-187.4769448</v>
+        <v>-192.3181546</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2147391202959829</v>
+        <v>0.2220842994392865</v>
       </c>
       <c r="T78">
-        <v>2.325510580400874</v>
+        <v>2.426619736070478</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0899799554452821</v>
+        <v>0.08881138459534339</v>
       </c>
       <c r="W78">
-        <v>0.2145827265060025</v>
+        <v>0.214858275512418</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.299933184817607</v>
+        <v>0.2960379486511446</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2165202610155978</v>
+        <v>0.2184202610155978</v>
       </c>
       <c r="C79">
-        <v>-1402.735478577302</v>
+        <v>-1440.971611738972</v>
       </c>
       <c r="D79">
-        <v>853.9645214226974</v>
+        <v>845.058388261028</v>
       </c>
       <c r="E79">
-        <v>1736.71</v>
+        <v>1766.04</v>
       </c>
       <c r="F79">
-        <v>2258.41</v>
+        <v>2287.74</v>
       </c>
       <c r="G79">
         <v>1.71</v>
@@ -7759,37 +7759,37 @@
         <v>157.65</v>
       </c>
       <c r="M79">
-        <v>532.5330779999999</v>
+        <v>539.4490920000001</v>
       </c>
       <c r="N79">
-        <v>-374.883078</v>
+        <v>-381.7990920000001</v>
       </c>
       <c r="O79">
-        <v>-112.4649234</v>
+        <v>-114.5397276</v>
       </c>
       <c r="P79">
-        <v>-262.4181546</v>
+        <v>-267.2593644000001</v>
       </c>
       <c r="Q79">
-        <v>-192.3181546</v>
+        <v>-197.1593644000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2220842994392865</v>
+        <v>0.2300972221410723</v>
       </c>
       <c r="T79">
-        <v>2.426619736070478</v>
+        <v>2.53692063316459</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08881138459534339</v>
+        <v>0.08767277710053127</v>
       </c>
       <c r="W79">
-        <v>0.214858275512418</v>
+        <v>0.2151267591596948</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2960379486511446</v>
+        <v>0.2922425903351042</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2184202610155978</v>
+        <v>0.2203202610155978</v>
       </c>
       <c r="C80">
-        <v>-1440.971611738972</v>
+        <v>-1479.023895310968</v>
       </c>
       <c r="D80">
-        <v>845.058388261028</v>
+        <v>836.3361046890323</v>
       </c>
       <c r="E80">
-        <v>1766.04</v>
+        <v>1795.37</v>
       </c>
       <c r="F80">
-        <v>2287.74</v>
+        <v>2317.07</v>
       </c>
       <c r="G80">
         <v>1.71</v>
@@ -7841,37 +7841,37 @@
         <v>157.65</v>
       </c>
       <c r="M80">
-        <v>539.4490920000001</v>
+        <v>546.3651060000001</v>
       </c>
       <c r="N80">
-        <v>-381.7990920000001</v>
+        <v>-388.7151060000001</v>
       </c>
       <c r="O80">
-        <v>-114.5397276</v>
+        <v>-116.6145318</v>
       </c>
       <c r="P80">
-        <v>-267.2593644000001</v>
+        <v>-272.1005742000001</v>
       </c>
       <c r="Q80">
-        <v>-197.1593644000001</v>
+        <v>-202.0005742000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2300972221410723</v>
+        <v>0.2388732803382662</v>
       </c>
       <c r="T80">
-        <v>2.53692063316459</v>
+        <v>2.657726377600999</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08767277710053127</v>
+        <v>0.08656299511191695</v>
       </c>
       <c r="W80">
-        <v>0.2151267591596948</v>
+        <v>0.21538844575261</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2922425903351042</v>
+        <v>0.2885433170397231</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2203202610155978</v>
+        <v>0.2222202610155978</v>
       </c>
       <c r="C81">
-        <v>-1479.023895310968</v>
+        <v>-1516.897963954422</v>
       </c>
       <c r="D81">
-        <v>836.3361046890323</v>
+        <v>827.7920360455778</v>
       </c>
       <c r="E81">
-        <v>1795.37</v>
+        <v>1824.7</v>
       </c>
       <c r="F81">
-        <v>2317.07</v>
+        <v>2346.4</v>
       </c>
       <c r="G81">
         <v>1.71</v>
@@ -7923,37 +7923,37 @@
         <v>157.65</v>
       </c>
       <c r="M81">
-        <v>546.3651060000001</v>
+        <v>553.28112</v>
       </c>
       <c r="N81">
-        <v>-388.7151060000001</v>
+        <v>-395.63112</v>
       </c>
       <c r="O81">
-        <v>-116.6145318</v>
+        <v>-118.689336</v>
       </c>
       <c r="P81">
-        <v>-272.1005742000001</v>
+        <v>-276.941784</v>
       </c>
       <c r="Q81">
-        <v>-202.0005742000001</v>
+        <v>-206.841784</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2388732803382662</v>
+        <v>0.2485269443551795</v>
       </c>
       <c r="T81">
-        <v>2.657726377600999</v>
+        <v>2.790612696481049</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08656299511191695</v>
+        <v>0.085480957673018</v>
       </c>
       <c r="W81">
-        <v>0.21538844575261</v>
+        <v>0.2156435901807024</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2885433170397231</v>
+        <v>0.2849365255767267</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2222202610155978</v>
+        <v>0.2241202610155978</v>
       </c>
       <c r="C82">
-        <v>-1516.897963954422</v>
+        <v>-1554.599224402613</v>
       </c>
       <c r="D82">
-        <v>827.7920360455778</v>
+        <v>819.4207755973872</v>
       </c>
       <c r="E82">
-        <v>1824.7</v>
+        <v>1854.03</v>
       </c>
       <c r="F82">
-        <v>2346.4</v>
+        <v>2375.73</v>
       </c>
       <c r="G82">
         <v>1.71</v>
@@ -8005,37 +8005,37 @@
         <v>157.65</v>
       </c>
       <c r="M82">
-        <v>553.28112</v>
+        <v>560.197134</v>
       </c>
       <c r="N82">
-        <v>-395.63112</v>
+        <v>-402.547134</v>
       </c>
       <c r="O82">
-        <v>-118.689336</v>
+        <v>-120.7641402</v>
       </c>
       <c r="P82">
-        <v>-276.941784</v>
+        <v>-281.7829938</v>
       </c>
       <c r="Q82">
-        <v>-206.841784</v>
+        <v>-211.6829938</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2485269443551795</v>
+        <v>0.2591967835317679</v>
       </c>
       <c r="T82">
-        <v>2.790612696481049</v>
+        <v>2.937487048927421</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.085480957673018</v>
+        <v>0.084425637207919</v>
       </c>
       <c r="W82">
-        <v>0.2156435901807024</v>
+        <v>0.2158924347463727</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2849365255767267</v>
+        <v>0.2814187906930634</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2241202610155978</v>
+        <v>0.2260202610155978</v>
       </c>
       <c r="C83">
-        <v>-1554.599224402613</v>
+        <v>-1592.132866870475</v>
       </c>
       <c r="D83">
-        <v>819.4207755973872</v>
+        <v>811.217133129525</v>
       </c>
       <c r="E83">
-        <v>1854.03</v>
+        <v>1883.36</v>
       </c>
       <c r="F83">
-        <v>2375.73</v>
+        <v>2405.06</v>
       </c>
       <c r="G83">
         <v>1.71</v>
@@ -8087,37 +8087,37 @@
         <v>157.65</v>
       </c>
       <c r="M83">
-        <v>560.197134</v>
+        <v>567.1131480000001</v>
       </c>
       <c r="N83">
-        <v>-402.547134</v>
+        <v>-409.4631480000002</v>
       </c>
       <c r="O83">
-        <v>-120.7641402</v>
+        <v>-122.8389444</v>
       </c>
       <c r="P83">
-        <v>-281.7829938</v>
+        <v>-286.6242036000001</v>
       </c>
       <c r="Q83">
-        <v>-211.6829938</v>
+        <v>-216.5242036000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2591967835317679</v>
+        <v>0.2710521603946439</v>
       </c>
       <c r="T83">
-        <v>2.937487048927421</v>
+        <v>3.100680773867833</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.084425637207919</v>
+        <v>0.083396056266359</v>
       </c>
       <c r="W83">
-        <v>0.2158924347463727</v>
+        <v>0.2161352099323925</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2814187906930634</v>
+        <v>0.2779868542211967</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2260202610155978</v>
+        <v>0.2279202610155978</v>
       </c>
       <c r="C84">
-        <v>-1592.132866870475</v>
+        <v>-1629.503875785553</v>
       </c>
       <c r="D84">
-        <v>811.217133129525</v>
+        <v>803.1761242144474</v>
       </c>
       <c r="E84">
-        <v>1883.36</v>
+        <v>1912.69</v>
       </c>
       <c r="F84">
-        <v>2405.06</v>
+        <v>2434.39</v>
       </c>
       <c r="G84">
         <v>1.71</v>
@@ -8169,37 +8169,37 @@
         <v>157.65</v>
       </c>
       <c r="M84">
-        <v>567.1131480000001</v>
+        <v>574.0291620000002</v>
       </c>
       <c r="N84">
-        <v>-409.4631480000002</v>
+        <v>-416.3791620000002</v>
       </c>
       <c r="O84">
-        <v>-122.8389444</v>
+        <v>-124.9137486</v>
       </c>
       <c r="P84">
-        <v>-286.6242036000001</v>
+        <v>-291.4654134000001</v>
       </c>
       <c r="Q84">
-        <v>-216.5242036000001</v>
+        <v>-221.3654134000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2710521603946439</v>
+        <v>0.2843022874766818</v>
       </c>
       <c r="T84">
-        <v>3.100680773867833</v>
+        <v>3.283073760565941</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.083396056266359</v>
+        <v>0.0823912845041137</v>
       </c>
       <c r="W84">
-        <v>0.2161352099323925</v>
+        <v>0.21637213511393</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2779868542211967</v>
+        <v>0.2746376150137124</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2279202610155978</v>
+        <v>0.2298202610155978</v>
       </c>
       <c r="C85">
-        <v>-1629.503875785553</v>
+        <v>-1666.717039887002</v>
       </c>
       <c r="D85">
-        <v>803.1761242144474</v>
+        <v>795.292960112998</v>
       </c>
       <c r="E85">
-        <v>1912.69</v>
+        <v>1942.02</v>
       </c>
       <c r="F85">
-        <v>2434.39</v>
+        <v>2463.72</v>
       </c>
       <c r="G85">
         <v>1.71</v>
@@ -8251,37 +8251,37 @@
         <v>157.65</v>
       </c>
       <c r="M85">
-        <v>574.0291620000002</v>
+        <v>580.9451760000001</v>
       </c>
       <c r="N85">
-        <v>-416.3791620000002</v>
+        <v>-423.2951760000001</v>
       </c>
       <c r="O85">
-        <v>-124.9137486</v>
+        <v>-126.9885528</v>
       </c>
       <c r="P85">
-        <v>-291.4654134000001</v>
+        <v>-296.3066232</v>
       </c>
       <c r="Q85">
-        <v>-221.3654134000001</v>
+        <v>-226.2066232000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2843022874766818</v>
+        <v>0.2992086804439745</v>
       </c>
       <c r="T85">
-        <v>3.283073760565941</v>
+        <v>3.488265870601313</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0823912845041137</v>
+        <v>0.08141043587906475</v>
       </c>
       <c r="W85">
-        <v>0.21637213511393</v>
+        <v>0.2166034192197165</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2746376150137124</v>
+        <v>0.2713681195968826</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2298202610155978</v>
+        <v>0.2317202610155978</v>
       </c>
       <c r="C86">
-        <v>-1666.717039887002</v>
+        <v>-1703.776961735645</v>
       </c>
       <c r="D86">
-        <v>795.2929601129982</v>
+        <v>787.563038264355</v>
       </c>
       <c r="E86">
-        <v>1942.02</v>
+        <v>1971.35</v>
       </c>
       <c r="F86">
-        <v>2463.72</v>
+        <v>2493.05</v>
       </c>
       <c r="G86">
         <v>1.71</v>
@@ -8333,37 +8333,37 @@
         <v>157.65</v>
       </c>
       <c r="M86">
-        <v>580.9451759999999</v>
+        <v>587.86119</v>
       </c>
       <c r="N86">
-        <v>-423.295176</v>
+        <v>-430.21119</v>
       </c>
       <c r="O86">
-        <v>-126.9885528</v>
+        <v>-129.063357</v>
       </c>
       <c r="P86">
-        <v>-296.3066232</v>
+        <v>-301.147833</v>
       </c>
       <c r="Q86">
-        <v>-226.2066232</v>
+        <v>-231.047833</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2992086804439743</v>
+        <v>0.3161025924735726</v>
       </c>
       <c r="T86">
-        <v>3.48826587060131</v>
+        <v>3.720816928641398</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08141043587906477</v>
+        <v>0.08045266604519341</v>
       </c>
       <c r="W86">
-        <v>0.2166034192197165</v>
+        <v>0.2168292613465434</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2713681195968826</v>
+        <v>0.268175553483978</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2317202610155978</v>
+        <v>0.2336202610155978</v>
       </c>
       <c r="C87">
-        <v>-1703.776961735645</v>
+        <v>-1740.688066674762</v>
       </c>
       <c r="D87">
-        <v>787.563038264355</v>
+        <v>779.9819333252376</v>
       </c>
       <c r="E87">
-        <v>1971.35</v>
+        <v>2000.68</v>
       </c>
       <c r="F87">
-        <v>2493.05</v>
+        <v>2522.38</v>
       </c>
       <c r="G87">
         <v>1.71</v>
@@ -8415,37 +8415,37 @@
         <v>157.65</v>
       </c>
       <c r="M87">
-        <v>587.86119</v>
+        <v>594.7772040000001</v>
       </c>
       <c r="N87">
-        <v>-430.21119</v>
+        <v>-437.1272040000001</v>
       </c>
       <c r="O87">
-        <v>-129.063357</v>
+        <v>-131.1381612</v>
       </c>
       <c r="P87">
-        <v>-301.147833</v>
+        <v>-305.9890428000001</v>
       </c>
       <c r="Q87">
-        <v>-231.047833</v>
+        <v>-235.8890428000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3161025924735726</v>
+        <v>0.3354099205073992</v>
       </c>
       <c r="T87">
-        <v>3.720816928641398</v>
+        <v>3.986589566401498</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08045266604519341</v>
+        <v>0.07951716992838882</v>
       </c>
       <c r="W87">
-        <v>0.2168292613465434</v>
+        <v>0.2170498513308859</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.268175553483978</v>
+        <v>0.2650572330946294</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2336202610155978</v>
+        <v>0.2355202610155978</v>
       </c>
       <c r="C88">
-        <v>-1740.688066674762</v>
+        <v>-1777.454611278275</v>
       </c>
       <c r="D88">
-        <v>779.9819333252376</v>
+        <v>772.5453887217255</v>
       </c>
       <c r="E88">
-        <v>2000.68</v>
+        <v>2030.01</v>
       </c>
       <c r="F88">
-        <v>2522.38</v>
+        <v>2551.71</v>
       </c>
       <c r="G88">
         <v>1.71</v>
@@ -8497,37 +8497,37 @@
         <v>157.65</v>
       </c>
       <c r="M88">
-        <v>594.7772040000001</v>
+        <v>601.693218</v>
       </c>
       <c r="N88">
-        <v>-437.1272040000001</v>
+        <v>-444.043218</v>
       </c>
       <c r="O88">
-        <v>-131.1381612</v>
+        <v>-133.2129654</v>
       </c>
       <c r="P88">
-        <v>-305.9890428000001</v>
+        <v>-310.8302526</v>
       </c>
       <c r="Q88">
-        <v>-235.8890428000001</v>
+        <v>-240.7302526</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3354099205073992</v>
+        <v>0.357687606700276</v>
       </c>
       <c r="T88">
-        <v>3.986589566401498</v>
+        <v>4.293250302278536</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07951716992838882</v>
+        <v>0.07860317946944184</v>
       </c>
       <c r="W88">
-        <v>0.2170498513308859</v>
+        <v>0.2172653702811056</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2650572330946294</v>
+        <v>0.2620105982314728</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2355202610155978</v>
+        <v>0.2374202610155978</v>
       </c>
       <c r="C89">
-        <v>-1777.454611278275</v>
+        <v>-1814.08069132021</v>
       </c>
       <c r="D89">
-        <v>772.5453887217255</v>
+        <v>765.2493086797905</v>
       </c>
       <c r="E89">
-        <v>2030.01</v>
+        <v>2059.34</v>
       </c>
       <c r="F89">
-        <v>2551.71</v>
+        <v>2581.04</v>
       </c>
       <c r="G89">
         <v>1.71</v>
@@ -8579,37 +8579,37 @@
         <v>157.65</v>
       </c>
       <c r="M89">
-        <v>601.693218</v>
+        <v>608.609232</v>
       </c>
       <c r="N89">
-        <v>-444.043218</v>
+        <v>-450.959232</v>
       </c>
       <c r="O89">
-        <v>-133.2129654</v>
+        <v>-135.2877696</v>
       </c>
       <c r="P89">
-        <v>-310.8302526</v>
+        <v>-315.6714624</v>
       </c>
       <c r="Q89">
-        <v>-240.7302526</v>
+        <v>-245.5714624</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.357687606700276</v>
+        <v>0.3836782405919658</v>
       </c>
       <c r="T89">
-        <v>4.293250302278536</v>
+        <v>4.651021160801748</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07860317946944184</v>
+        <v>0.07770996152092545</v>
       </c>
       <c r="W89">
-        <v>0.2172653702811056</v>
+        <v>0.2174759910733658</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2620105982314728</v>
+        <v>0.2590332050697515</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2374202610155978</v>
+        <v>0.2393202610155978</v>
       </c>
       <c r="C90">
-        <v>-1814.08069132021</v>
+        <v>-1850.5702492968</v>
       </c>
       <c r="D90">
-        <v>765.2493086797905</v>
+        <v>758.0897507031998</v>
       </c>
       <c r="E90">
-        <v>2059.34</v>
+        <v>2088.67</v>
       </c>
       <c r="F90">
-        <v>2581.04</v>
+        <v>2610.37</v>
       </c>
       <c r="G90">
         <v>1.71</v>
@@ -8661,37 +8661,37 @@
         <v>157.65</v>
       </c>
       <c r="M90">
-        <v>608.609232</v>
+        <v>615.525246</v>
       </c>
       <c r="N90">
-        <v>-450.959232</v>
+        <v>-457.8752460000001</v>
       </c>
       <c r="O90">
-        <v>-135.2877696</v>
+        <v>-137.3625738</v>
       </c>
       <c r="P90">
-        <v>-315.6714624</v>
+        <v>-320.5126722000001</v>
       </c>
       <c r="Q90">
-        <v>-245.5714624</v>
+        <v>-250.4126722000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3836782405919658</v>
+        <v>0.4143944442821445</v>
       </c>
       <c r="T90">
-        <v>4.651021160801748</v>
+        <v>5.073841266329181</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07770996152092545</v>
+        <v>0.07683681588585888</v>
       </c>
       <c r="W90">
-        <v>0.2174759910733658</v>
+        <v>0.2176818788141145</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2590332050697515</v>
+        <v>0.2561227196195296</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2393202610155978</v>
+        <v>0.2412202610155978</v>
       </c>
       <c r="C91">
-        <v>-1850.5702492968</v>
+        <v>-1886.927081530244</v>
       </c>
       <c r="D91">
-        <v>758.0897507031998</v>
+        <v>751.062918469756</v>
       </c>
       <c r="E91">
-        <v>2088.67</v>
+        <v>2118</v>
       </c>
       <c r="F91">
-        <v>2610.37</v>
+        <v>2639.7</v>
       </c>
       <c r="G91">
         <v>1.71</v>
@@ -8743,37 +8743,37 @@
         <v>157.65</v>
       </c>
       <c r="M91">
-        <v>615.525246</v>
+        <v>622.4412600000001</v>
       </c>
       <c r="N91">
-        <v>-457.8752460000001</v>
+        <v>-464.7912600000001</v>
       </c>
       <c r="O91">
-        <v>-137.3625738</v>
+        <v>-139.437378</v>
       </c>
       <c r="P91">
-        <v>-320.5126722000001</v>
+        <v>-325.3538820000001</v>
       </c>
       <c r="Q91">
-        <v>-250.4126722000001</v>
+        <v>-255.2538820000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4143944442821445</v>
+        <v>0.4512538887103589</v>
       </c>
       <c r="T91">
-        <v>5.073841266329181</v>
+        <v>5.581225392962098</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07683681588585888</v>
+        <v>0.07598307348712711</v>
       </c>
       <c r="W91">
-        <v>0.2176818788141145</v>
+        <v>0.2178831912717354</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2561227196195296</v>
+        <v>0.253276911623757</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2412202610155978</v>
+        <v>0.2431202610155978</v>
       </c>
       <c r="C92">
-        <v>-1886.927081530244</v>
+        <v>-1923.154844881015</v>
       </c>
       <c r="D92">
-        <v>751.062918469756</v>
+        <v>744.1651551189848</v>
       </c>
       <c r="E92">
-        <v>2118</v>
+        <v>2147.33</v>
       </c>
       <c r="F92">
-        <v>2639.7</v>
+        <v>2669.03</v>
       </c>
       <c r="G92">
         <v>1.71</v>
@@ -8825,37 +8825,37 @@
         <v>157.65</v>
       </c>
       <c r="M92">
-        <v>622.4412600000001</v>
+        <v>629.3572740000001</v>
       </c>
       <c r="N92">
-        <v>-464.7912600000001</v>
+        <v>-471.7072740000001</v>
       </c>
       <c r="O92">
-        <v>-139.437378</v>
+        <v>-141.5121822</v>
       </c>
       <c r="P92">
-        <v>-325.3538820000001</v>
+        <v>-330.1950918000001</v>
       </c>
       <c r="Q92">
-        <v>-255.2538820000001</v>
+        <v>-260.0950918000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4512538887103589</v>
+        <v>0.4963043207892878</v>
       </c>
       <c r="T92">
-        <v>5.581225392962098</v>
+        <v>6.201361547735666</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07598307348712711</v>
+        <v>0.07514809465759822</v>
       </c>
       <c r="W92">
-        <v>0.2178831912717354</v>
+        <v>0.2180800792797384</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.253276911623757</v>
+        <v>0.2504936488586608</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2431202610155978</v>
+        <v>0.2450202610155978</v>
       </c>
       <c r="C93">
-        <v>-1923.154844881015</v>
+        <v>-1959.257063093669</v>
       </c>
       <c r="D93">
-        <v>744.1651551189848</v>
+        <v>737.3929369063306</v>
       </c>
       <c r="E93">
-        <v>2147.33</v>
+        <v>2176.66</v>
       </c>
       <c r="F93">
-        <v>2669.03</v>
+        <v>2698.36</v>
       </c>
       <c r="G93">
         <v>1.71</v>
@@ -8907,37 +8907,37 @@
         <v>157.65</v>
       </c>
       <c r="M93">
-        <v>629.3572740000001</v>
+        <v>636.2732880000001</v>
       </c>
       <c r="N93">
-        <v>-471.7072740000001</v>
+        <v>-478.6232880000001</v>
       </c>
       <c r="O93">
-        <v>-141.5121822</v>
+        <v>-143.5869864</v>
       </c>
       <c r="P93">
-        <v>-330.1950918000001</v>
+        <v>-335.0363016000001</v>
       </c>
       <c r="Q93">
-        <v>-260.0950918000001</v>
+        <v>-264.9363016000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4963043207892878</v>
+        <v>0.5526173608879489</v>
       </c>
       <c r="T93">
-        <v>6.201361547735666</v>
+        <v>6.976531741202626</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07514809465759822</v>
+        <v>0.07433126754175477</v>
       </c>
       <c r="W93">
-        <v>0.2180800792797384</v>
+        <v>0.2182726871136542</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2504936488586608</v>
+        <v>0.2477708918058492</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2450202610155978</v>
+        <v>0.2469202610155978</v>
       </c>
       <c r="C94">
-        <v>-1959.257063093669</v>
+        <v>-1995.237132799275</v>
       </c>
       <c r="D94">
-        <v>737.3929369063306</v>
+        <v>730.7428672007253</v>
       </c>
       <c r="E94">
-        <v>2176.66</v>
+        <v>2205.99</v>
       </c>
       <c r="F94">
-        <v>2698.36</v>
+        <v>2727.69</v>
       </c>
       <c r="G94">
         <v>1.71</v>
@@ -8989,37 +8989,37 @@
         <v>157.65</v>
       </c>
       <c r="M94">
-        <v>636.2732880000001</v>
+        <v>643.189302</v>
       </c>
       <c r="N94">
-        <v>-478.6232880000001</v>
+        <v>-485.539302</v>
       </c>
       <c r="O94">
-        <v>-143.5869864</v>
+        <v>-145.6617906</v>
       </c>
       <c r="P94">
-        <v>-335.0363016000001</v>
+        <v>-339.8775114</v>
       </c>
       <c r="Q94">
-        <v>-264.9363016000001</v>
+        <v>-269.7775114</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5526173608879489</v>
+        <v>0.6250198410147988</v>
       </c>
       <c r="T94">
-        <v>6.976531741202626</v>
+        <v>7.973179132803002</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07433126754175477</v>
+        <v>0.07353200660044559</v>
       </c>
       <c r="W94">
-        <v>0.2182726871136542</v>
+        <v>0.2184611528436149</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2477708918058492</v>
+        <v>0.245106688668152</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2469202610155978</v>
+        <v>0.2488202610155978</v>
       </c>
       <c r="C95">
-        <v>-1995.237132799275</v>
+        <v>-2031.098329195954</v>
       </c>
       <c r="D95">
-        <v>730.7428672007253</v>
+        <v>724.2116708040459</v>
       </c>
       <c r="E95">
-        <v>2205.99</v>
+        <v>2235.32</v>
       </c>
       <c r="F95">
-        <v>2727.69</v>
+        <v>2757.02</v>
       </c>
       <c r="G95">
         <v>1.71</v>
@@ -9071,37 +9071,37 @@
         <v>157.65</v>
       </c>
       <c r="M95">
-        <v>643.189302</v>
+        <v>650.105316</v>
       </c>
       <c r="N95">
-        <v>-485.539302</v>
+        <v>-492.455316</v>
       </c>
       <c r="O95">
-        <v>-145.6617906</v>
+        <v>-147.7365948</v>
       </c>
       <c r="P95">
-        <v>-339.8775114</v>
+        <v>-344.7187212</v>
       </c>
       <c r="Q95">
-        <v>-269.7775114</v>
+        <v>-274.6187212</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6250198410147988</v>
+        <v>0.721556481183932</v>
       </c>
       <c r="T95">
-        <v>7.973179132803002</v>
+        <v>9.302042321603505</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07353200660044559</v>
+        <v>0.07274975121107914</v>
       </c>
       <c r="W95">
-        <v>0.2184611528436149</v>
+        <v>0.2186456086644275</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.245106688668152</v>
+        <v>0.2424991707035972</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2488202610155978</v>
+        <v>0.2507202610155978</v>
       </c>
       <c r="C96">
-        <v>-2031.098329195954</v>
+        <v>-2066.8438114275</v>
       </c>
       <c r="D96">
-        <v>724.2116708040459</v>
+        <v>717.7961885724997</v>
       </c>
       <c r="E96">
-        <v>2235.32</v>
+        <v>2264.650000000001</v>
       </c>
       <c r="F96">
-        <v>2757.02</v>
+        <v>2786.35</v>
       </c>
       <c r="G96">
         <v>1.71</v>
@@ -9153,37 +9153,37 @@
         <v>157.65</v>
       </c>
       <c r="M96">
-        <v>650.105316</v>
+        <v>657.0213300000001</v>
       </c>
       <c r="N96">
-        <v>-492.455316</v>
+        <v>-499.3713300000002</v>
       </c>
       <c r="O96">
-        <v>-147.7365948</v>
+        <v>-149.8113990000001</v>
       </c>
       <c r="P96">
-        <v>-344.7187212</v>
+        <v>-349.5599310000001</v>
       </c>
       <c r="Q96">
-        <v>-274.6187212</v>
+        <v>-279.4599310000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.721556481183932</v>
+        <v>0.8567077774207188</v>
       </c>
       <c r="T96">
-        <v>9.302042321603505</v>
+        <v>11.16245078592421</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07274975121107914</v>
+        <v>0.07198396435622567</v>
       </c>
       <c r="W96">
-        <v>0.2186456086644275</v>
+        <v>0.218826181204802</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2424991707035972</v>
+        <v>0.2399465478540855</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2507202610155978</v>
+        <v>0.2526202610155978</v>
       </c>
       <c r="C97">
-        <v>-2066.8438114275</v>
+        <v>-2102.476627678615</v>
       </c>
       <c r="D97">
-        <v>717.7961885724997</v>
+        <v>711.4933723213852</v>
       </c>
       <c r="E97">
-        <v>2264.650000000001</v>
+        <v>2293.98</v>
       </c>
       <c r="F97">
-        <v>2786.35</v>
+        <v>2815.68</v>
       </c>
       <c r="G97">
         <v>1.71</v>
@@ -9235,37 +9235,37 @@
         <v>157.65</v>
       </c>
       <c r="M97">
-        <v>657.0213300000001</v>
+        <v>663.9373440000001</v>
       </c>
       <c r="N97">
-        <v>-499.3713300000002</v>
+        <v>-506.2873440000001</v>
       </c>
       <c r="O97">
-        <v>-149.8113990000001</v>
+        <v>-151.8862032</v>
       </c>
       <c r="P97">
-        <v>-349.5599310000001</v>
+        <v>-354.4011408000001</v>
       </c>
       <c r="Q97">
-        <v>-279.4599310000001</v>
+        <v>-284.3011408000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8567077774207188</v>
+        <v>1.059434721775899</v>
       </c>
       <c r="T97">
-        <v>11.16245078592421</v>
+        <v>13.95306348240527</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07198396435622567</v>
+        <v>0.07123413139418165</v>
       </c>
       <c r="W97">
-        <v>0.218826181204802</v>
+        <v>0.219002991817252</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2399465478540855</v>
+        <v>0.2374471046472723</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2526202610155978</v>
+        <v>0.2545202610155978</v>
       </c>
       <c r="C98">
-        <v>-2102.476627678614</v>
+        <v>-2137.999720004048</v>
       </c>
       <c r="D98">
-        <v>711.4933723213852</v>
+        <v>705.3002799959512</v>
       </c>
       <c r="E98">
-        <v>2293.98</v>
+        <v>2323.309999999999</v>
       </c>
       <c r="F98">
-        <v>2815.68</v>
+        <v>2845.01</v>
       </c>
       <c r="G98">
         <v>1.71</v>
@@ -9317,37 +9317,37 @@
         <v>157.65</v>
       </c>
       <c r="M98">
-        <v>663.9373439999999</v>
+        <v>670.853358</v>
       </c>
       <c r="N98">
-        <v>-506.287344</v>
+        <v>-513.203358</v>
       </c>
       <c r="O98">
-        <v>-151.8862032</v>
+        <v>-153.9610074</v>
       </c>
       <c r="P98">
-        <v>-354.4011408</v>
+        <v>-359.2423506</v>
       </c>
       <c r="Q98">
-        <v>-284.3011408</v>
+        <v>-289.1423506</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.059434721775896</v>
+        <v>1.397312962367862</v>
       </c>
       <c r="T98">
-        <v>13.95306348240523</v>
+        <v>18.60408464320698</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07123413139418168</v>
+        <v>0.07049975890558186</v>
       </c>
       <c r="W98">
-        <v>0.219002991817252</v>
+        <v>0.2191761568500638</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2374471046472723</v>
+        <v>0.2349991963519396</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2545202610155978</v>
+        <v>0.2564202610155978</v>
       </c>
       <c r="C99">
-        <v>-2137.999720004048</v>
+        <v>-2173.415928907708</v>
       </c>
       <c r="D99">
-        <v>705.3002799959512</v>
+        <v>699.2140710922918</v>
       </c>
       <c r="E99">
-        <v>2323.309999999999</v>
+        <v>2352.64</v>
       </c>
       <c r="F99">
-        <v>2845.01</v>
+        <v>2874.34</v>
       </c>
       <c r="G99">
         <v>1.71</v>
@@ -9399,37 +9399,37 @@
         <v>157.65</v>
       </c>
       <c r="M99">
-        <v>670.853358</v>
+        <v>677.7693720000001</v>
       </c>
       <c r="N99">
-        <v>-513.203358</v>
+        <v>-520.1193720000001</v>
       </c>
       <c r="O99">
-        <v>-153.9610074</v>
+        <v>-156.0358116</v>
       </c>
       <c r="P99">
-        <v>-359.2423506</v>
+        <v>-364.0835604000001</v>
       </c>
       <c r="Q99">
-        <v>-289.1423506</v>
+        <v>-293.9835604000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.397312962367862</v>
+        <v>2.073069443551792</v>
       </c>
       <c r="T99">
-        <v>18.60408464320698</v>
+        <v>27.90612696481046</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07049975890558186</v>
+        <v>0.06978037361062693</v>
       </c>
       <c r="W99">
-        <v>0.2191761568500638</v>
+        <v>0.2193457879026142</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2349991963519396</v>
+        <v>0.2326012453687565</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2564202610155978</v>
+        <v>0.2583202610155978</v>
       </c>
       <c r="C100">
-        <v>-2173.415928907708</v>
+        <v>-2208.727997686704</v>
       </c>
       <c r="D100">
-        <v>699.2140710922918</v>
+        <v>693.2320023132958</v>
       </c>
       <c r="E100">
-        <v>2352.64</v>
+        <v>2381.97</v>
       </c>
       <c r="F100">
-        <v>2874.34</v>
+        <v>2903.67</v>
       </c>
       <c r="G100">
         <v>1.71</v>
@@ -9481,37 +9481,37 @@
         <v>157.65</v>
       </c>
       <c r="M100">
-        <v>677.7693720000001</v>
+        <v>684.685386</v>
       </c>
       <c r="N100">
-        <v>-520.1193720000001</v>
+        <v>-527.035386</v>
       </c>
       <c r="O100">
-        <v>-156.0358116</v>
+        <v>-158.1106158</v>
       </c>
       <c r="P100">
-        <v>-364.0835604000001</v>
+        <v>-368.9247702</v>
       </c>
       <c r="Q100">
-        <v>-293.9835604000001</v>
+        <v>-298.8247702</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.073069443551792</v>
+        <v>4.100338887103585</v>
       </c>
       <c r="T100">
-        <v>27.90612696481046</v>
+        <v>55.81225392962093</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06978037361062693</v>
+        <v>0.06907552135193373</v>
       </c>
       <c r="W100">
-        <v>0.2193457879026142</v>
+        <v>0.219511992065214</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2326012453687565</v>
+        <v>0.2302517378397791</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2583202610155978</v>
-      </c>
-      <c r="C101">
-        <v>-2208.727997686704</v>
-      </c>
-      <c r="D101">
-        <v>693.2320023132958</v>
-      </c>
-      <c r="E101">
-        <v>2381.97</v>
-      </c>
-      <c r="F101">
-        <v>2903.67</v>
-      </c>
-      <c r="G101">
-        <v>1.71</v>
-      </c>
-      <c r="H101">
-        <v>2411.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>227.75</v>
-      </c>
-      <c r="K101">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="L101">
-        <v>157.65</v>
-      </c>
-      <c r="M101">
-        <v>684.685386</v>
-      </c>
-      <c r="N101">
-        <v>-527.035386</v>
-      </c>
-      <c r="O101">
-        <v>-158.1106158</v>
-      </c>
-      <c r="P101">
-        <v>-368.9247702</v>
-      </c>
-      <c r="Q101">
-        <v>-298.8247702</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.100338887103585</v>
-      </c>
-      <c r="T101">
-        <v>55.81225392962093</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06907552135193373</v>
-      </c>
-      <c r="W101">
-        <v>0.219511992065214</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2302517378397791</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
